--- a/outputs/tower_output.xlsx
+++ b/outputs/tower_output.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E433"/>
+  <dimension ref="A1:E435"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,10 +471,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D2" t="n">
+        <v>0</v>
       </c>
       <c r="E2" t="inlineStr"/>
     </row>
@@ -494,10 +492,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>[4.5]</t>
-        </is>
+      <c r="D3" t="n">
+        <v>4.5</v>
       </c>
       <c r="E3" t="inlineStr"/>
     </row>
@@ -517,10 +513,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D4" t="n">
+        <v>0</v>
       </c>
       <c r="E4" t="inlineStr"/>
     </row>
@@ -540,10 +534,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>[2.9]</t>
-        </is>
+      <c r="D5" t="n">
+        <v>2.9</v>
       </c>
       <c r="E5" t="inlineStr"/>
     </row>
@@ -563,10 +555,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D6" t="n">
+        <v>0</v>
       </c>
       <c r="E6" t="inlineStr"/>
     </row>
@@ -586,10 +576,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>[14.6]</t>
-        </is>
+      <c r="D7" t="n">
+        <v>14.6</v>
       </c>
       <c r="E7" t="inlineStr"/>
     </row>
@@ -609,10 +597,8 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D8" t="n">
+        <v>0</v>
       </c>
       <c r="E8" t="inlineStr"/>
     </row>
@@ -632,10 +618,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D9" t="n">
+        <v>0</v>
       </c>
       <c r="E9" t="inlineStr"/>
     </row>
@@ -655,10 +639,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>[3.6254]</t>
-        </is>
+      <c r="D10" t="n">
+        <v>3.6254</v>
       </c>
       <c r="E10" t="inlineStr"/>
     </row>
@@ -678,10 +660,8 @@
           <t>kW</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>[5000.]</t>
-        </is>
+      <c r="D11" t="n">
+        <v>5000</v>
       </c>
       <c r="E11" t="inlineStr"/>
     </row>
@@ -701,10 +681,8 @@
           <t>USD/kW</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>[21.15]</t>
-        </is>
+      <c r="D12" t="n">
+        <v>21.15</v>
       </c>
       <c r="E12" t="inlineStr"/>
     </row>
@@ -724,10 +702,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D13" t="n">
+        <v>0</v>
       </c>
       <c r="E13" t="inlineStr"/>
     </row>
@@ -747,10 +723,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>[18.8]</t>
-        </is>
+      <c r="D14" t="n">
+        <v>18.8</v>
       </c>
       <c r="E14" t="inlineStr"/>
     </row>
@@ -770,10 +744,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D15" t="n">
+        <v>0</v>
       </c>
       <c r="E15" t="inlineStr"/>
     </row>
@@ -793,10 +765,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>[5.7]</t>
-        </is>
+      <c r="D16" t="n">
+        <v>5.7</v>
       </c>
       <c r="E16" t="inlineStr"/>
     </row>
@@ -816,10 +786,8 @@
           <t>USD/kW</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>[41.85]</t>
-        </is>
+      <c r="D17" t="n">
+        <v>41.85</v>
       </c>
       <c r="E17" t="inlineStr"/>
     </row>
@@ -839,10 +807,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D18" t="n">
+        <v>0</v>
       </c>
       <c r="E18" t="inlineStr"/>
     </row>
@@ -862,10 +828,8 @@
           <t>N*m/kg</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>[200.]</t>
-        </is>
+      <c r="D19" t="n">
+        <v>200</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -889,10 +853,8 @@
           <t>USD/kN/m</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>[50.]</t>
-        </is>
+      <c r="D20" t="n">
+        <v>50</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -916,10 +878,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D21" t="n">
+        <v>0</v>
       </c>
       <c r="E21" t="inlineStr"/>
     </row>
@@ -939,10 +899,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>[12.4]</t>
-        </is>
+      <c r="D22" t="n">
+        <v>12.4</v>
       </c>
       <c r="E22" t="inlineStr"/>
     </row>
@@ -962,10 +920,8 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D23" t="n">
+        <v>0</v>
       </c>
       <c r="E23" t="inlineStr"/>
     </row>
@@ -985,10 +941,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D24" t="n">
+        <v>0</v>
       </c>
       <c r="E24" t="inlineStr"/>
     </row>
@@ -1008,10 +962,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>[6.8]</t>
-        </is>
+      <c r="D25" t="n">
+        <v>6.8</v>
       </c>
       <c r="E25" t="inlineStr"/>
     </row>
@@ -1031,10 +983,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D26" t="n">
+        <v>0</v>
       </c>
       <c r="E26" t="inlineStr"/>
     </row>
@@ -1054,10 +1004,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
       <c r="E27" t="inlineStr"/>
     </row>
@@ -1077,10 +1025,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D28" t="n">
+        <v>0</v>
       </c>
       <c r="E28" t="inlineStr"/>
     </row>
@@ -1096,10 +1042,8 @@
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D29" t="n">
+        <v>0</v>
       </c>
       <c r="E29" t="inlineStr"/>
     </row>
@@ -1115,10 +1059,8 @@
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D30" t="n">
+        <v>0</v>
       </c>
       <c r="E30" t="inlineStr"/>
     </row>
@@ -1134,10 +1076,8 @@
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D31" t="n">
+        <v>0</v>
       </c>
       <c r="E31" t="inlineStr"/>
     </row>
@@ -1153,10 +1093,8 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D32" t="n">
+        <v>0</v>
       </c>
       <c r="E32" t="inlineStr"/>
     </row>
@@ -1176,10 +1114,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>[3.9]</t>
-        </is>
+      <c r="D33" t="n">
+        <v>3.9</v>
       </c>
       <c r="E33" t="inlineStr"/>
     </row>
@@ -1199,10 +1135,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D34" t="n">
+        <v>0</v>
       </c>
       <c r="E34" t="inlineStr"/>
     </row>
@@ -1222,10 +1156,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>[124.]</t>
-        </is>
+      <c r="D35" t="n">
+        <v>124</v>
       </c>
       <c r="E35" t="inlineStr"/>
     </row>
@@ -1245,10 +1177,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D36" t="n">
+        <v>0</v>
       </c>
       <c r="E36" t="inlineStr"/>
     </row>
@@ -1268,10 +1198,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>[11.9]</t>
-        </is>
+      <c r="D37" t="n">
+        <v>11.9</v>
       </c>
       <c r="E37" t="inlineStr"/>
     </row>
@@ -1291,10 +1219,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D38" t="n">
+        <v>0</v>
       </c>
       <c r="E38" t="inlineStr"/>
     </row>
@@ -1314,10 +1240,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D39" t="n">
+        <v>0</v>
       </c>
       <c r="E39" t="inlineStr"/>
     </row>
@@ -1337,10 +1261,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D40" t="n">
+        <v>0</v>
       </c>
       <c r="E40" t="inlineStr"/>
     </row>
@@ -1356,10 +1278,8 @@
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D41" t="n">
+        <v>0</v>
       </c>
       <c r="E41" t="inlineStr"/>
     </row>
@@ -1375,10 +1295,8 @@
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D42" t="n">
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr"/>
     </row>
@@ -1394,10 +1312,8 @@
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D43" t="n">
+        <v>0</v>
       </c>
       <c r="E43" t="inlineStr"/>
     </row>
@@ -1413,10 +1329,8 @@
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D44" t="n">
+        <v>0</v>
       </c>
       <c r="E44" t="inlineStr"/>
     </row>
@@ -1457,10 +1371,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>[22.1]</t>
-        </is>
+      <c r="D46" t="n">
+        <v>22.1</v>
       </c>
       <c r="E46" t="inlineStr"/>
     </row>
@@ -1480,10 +1392,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>[17.1]</t>
-        </is>
+      <c r="D47" t="n">
+        <v>17.1</v>
       </c>
       <c r="E47" t="inlineStr"/>
     </row>
@@ -1503,10 +1413,8 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>[12000.]</t>
-        </is>
+      <c r="D48" t="n">
+        <v>12000</v>
       </c>
       <c r="E48" t="inlineStr"/>
     </row>
@@ -1568,10 +1476,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>[11.1]</t>
-        </is>
+      <c r="D51" t="n">
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr"/>
     </row>
@@ -1587,10 +1493,8 @@
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D52" t="n">
+        <v>0</v>
       </c>
       <c r="E52" t="inlineStr"/>
     </row>
@@ -1606,10 +1510,8 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D53" t="n">
+        <v>0</v>
       </c>
       <c r="E53" t="inlineStr"/>
     </row>
@@ -1625,10 +1527,8 @@
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D54" t="n">
+        <v>0</v>
       </c>
       <c r="E54" t="inlineStr"/>
     </row>
@@ -1644,10 +1544,8 @@
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D55" t="n">
+        <v>0</v>
       </c>
       <c r="E55" t="inlineStr"/>
     </row>
@@ -1667,10 +1565,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>[2.9]</t>
-        </is>
+      <c r="D56" t="n">
+        <v>2.9</v>
       </c>
       <c r="E56" t="inlineStr"/>
     </row>
@@ -1690,10 +1586,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>[18.8]</t>
-        </is>
+      <c r="D57" t="n">
+        <v>18.8</v>
       </c>
       <c r="E57" t="inlineStr"/>
     </row>
@@ -1709,10 +1603,8 @@
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D58" t="n">
+        <v>0</v>
       </c>
       <c r="E58" t="inlineStr"/>
     </row>
@@ -1728,10 +1620,8 @@
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D59" t="n">
+        <v>0</v>
       </c>
       <c r="E59" t="inlineStr"/>
     </row>
@@ -1747,10 +1637,8 @@
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D60" t="n">
+        <v>0</v>
       </c>
       <c r="E60" t="inlineStr"/>
     </row>
@@ -1766,10 +1654,8 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D61" t="n">
+        <v>0</v>
       </c>
       <c r="E61" t="inlineStr"/>
     </row>
@@ -1789,10 +1675,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>[8.3]</t>
-        </is>
+      <c r="D62" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="E62" t="inlineStr"/>
     </row>
@@ -1814,7 +1698,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E63" t="inlineStr"/>
@@ -1837,7 +1721,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E64" t="inlineStr"/>
@@ -1860,7 +1744,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E65" t="inlineStr"/>
@@ -1883,7 +1767,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E66" t="inlineStr"/>
@@ -1906,7 +1790,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E67" t="inlineStr"/>
@@ -1927,10 +1811,8 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D68" t="n">
+        <v>0</v>
       </c>
       <c r="E68" t="inlineStr"/>
     </row>
@@ -1950,10 +1832,8 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D69" t="n">
+        <v>0</v>
       </c>
       <c r="E69" t="inlineStr"/>
     </row>
@@ -1973,10 +1853,8 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>[11.73732]</t>
-        </is>
+      <c r="D70" t="n">
+        <v>11.73732</v>
       </c>
       <c r="E70" t="inlineStr"/>
     </row>
@@ -1996,10 +1874,8 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D71" t="n">
+        <v>0</v>
       </c>
       <c r="E71" t="inlineStr"/>
     </row>
@@ -2015,10 +1891,8 @@
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>[0.2]</t>
-        </is>
+      <c r="D72" t="n">
+        <v>0.2</v>
       </c>
       <c r="E72" t="inlineStr"/>
     </row>
@@ -2038,10 +1912,8 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D73" t="n">
+        <v>0</v>
       </c>
       <c r="E73" t="inlineStr"/>
     </row>
@@ -2061,10 +1933,8 @@
           <t>kg/m**3</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>[1.225]</t>
-        </is>
+      <c r="D74" t="n">
+        <v>1.225</v>
       </c>
       <c r="E74" t="inlineStr"/>
     </row>
@@ -2084,10 +1954,8 @@
           <t>kg/m/s</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>[1.81e-05]</t>
-        </is>
+      <c r="D75" t="n">
+        <v>1.81e-05</v>
       </c>
       <c r="E75" t="inlineStr"/>
     </row>
@@ -2105,7 +1973,7 @@
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>[-1. -1. -1. -1. -1. -1. -1.]</t>
+          <t>[-1.0, -1.0, -1.0, -1.0, -1.0, -1.0, -1.0]</t>
         </is>
       </c>
       <c r="E76" t="inlineStr"/>
@@ -2128,7 +1996,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E77" t="inlineStr"/>
@@ -2151,7 +2019,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E78" t="inlineStr"/>
@@ -2174,7 +2042,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E79" t="inlineStr"/>
@@ -2197,7 +2065,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E80" t="inlineStr"/>
@@ -2220,7 +2088,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E81" t="inlineStr"/>
@@ -2241,10 +2109,8 @@
           <t>deg</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D82" t="n">
+        <v>0</v>
       </c>
       <c r="E82" t="inlineStr"/>
     </row>
@@ -2264,10 +2130,8 @@
           <t>m/s</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>[70.]</t>
-        </is>
+      <c r="D83" t="n">
+        <v>70</v>
       </c>
       <c r="E83" t="inlineStr"/>
     </row>
@@ -2285,7 +2149,7 @@
       <c r="C84" t="inlineStr"/>
       <c r="D84" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E84" t="inlineStr"/>
@@ -2306,10 +2170,8 @@
           <t>kg</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>[285598.8]</t>
-        </is>
+      <c r="D85" t="n">
+        <v>285598.8</v>
       </c>
       <c r="E85" t="inlineStr"/>
     </row>
@@ -2331,8 +2193,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>[1.14930678e+08 2.20354030e+07 1.87597425e+07 0.00000000e+00
- 5.03710467e+05 0.00000000e+00]</t>
+          <t>[114930678.0, 22035403.0, 18759742.5, 0.0, 503710.467, 0.0]</t>
         </is>
       </c>
       <c r="E86" t="inlineStr"/>
@@ -2355,7 +2216,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>[-1.13197635  0.          0.50875268]</t>
+          <t>[-1.13197635, 0.0, 0.50875268]</t>
         </is>
       </c>
       <c r="E87" t="inlineStr"/>
@@ -2378,9 +2239,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>[[ 1284744.19620519   930198.60063279]
- [       0.                0.        ]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[[1284744.19620519, 930198.60063279], [0.0, 0.0], [-2914124.84400512, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E88" t="inlineStr"/>
@@ -2403,9 +2262,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>[[ 3963732.76208099 -1683669.22411597]
- [-2275104.79420872 -2522475.34625363]
- [ -346781.68192839   147301.97023764]]</t>
+          <t>[[3963732.76208099, -1683669.22411597], [-2275104.79420872, -2522475.34625363], [-346781.68192839, 147301.97023764]]</t>
         </is>
       </c>
       <c r="E89" t="inlineStr"/>
@@ -2424,7 +2281,7 @@
       <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E90" t="inlineStr"/>
@@ -2443,7 +2300,7 @@
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E91" t="inlineStr"/>
@@ -2464,10 +2321,8 @@
           <t>kg/m**3</t>
         </is>
       </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D92" t="n">
+        <v>0</v>
       </c>
       <c r="E92" t="inlineStr"/>
     </row>
@@ -2483,10 +2338,8 @@
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D93" t="n">
+        <v>0</v>
       </c>
       <c r="E93" t="inlineStr"/>
     </row>
@@ -2502,10 +2355,8 @@
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>[1.]</t>
-        </is>
+      <c r="D94" t="n">
+        <v>1</v>
       </c>
       <c r="E94" t="inlineStr"/>
     </row>
@@ -2521,10 +2372,8 @@
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D95" t="n">
+        <v>0</v>
       </c>
       <c r="E95" t="inlineStr"/>
     </row>
@@ -2540,10 +2389,8 @@
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D96" t="n">
+        <v>0</v>
       </c>
       <c r="E96" t="inlineStr"/>
     </row>
@@ -2565,7 +2412,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>[[0.027  0.0222 0.019 ]]</t>
+          <t>[[0.027, 0.0222, 0.019000000000000003]]</t>
         </is>
       </c>
       <c r="E97" t="inlineStr"/>
@@ -2588,7 +2435,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>[6.    4.935 3.87 ]</t>
+          <t>[6.0, 4.935, 3.87]</t>
         </is>
       </c>
       <c r="E98" t="inlineStr"/>
@@ -2611,7 +2458,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>[[2.e+11 2.e+11 2.e+11]]</t>
+          <t>[[200000000000.0, 200000000000.0, 200000000000.0]]</t>
         </is>
       </c>
       <c r="E99" t="inlineStr"/>
@@ -2632,10 +2479,8 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D100" t="n">
+        <v>0</v>
       </c>
       <c r="E100" t="inlineStr"/>
     </row>
@@ -2657,7 +2502,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>[[7.93e+10 7.93e+10 7.93e+10]]</t>
+          <t>[[79300000000.0, 79300000000.0, 79300000000.0]]</t>
         </is>
       </c>
       <c r="E101" t="inlineStr"/>
@@ -2678,10 +2523,8 @@
           <t>Pa</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>[3.45e+08]</t>
-        </is>
+      <c r="D102" t="n">
+        <v>345000000</v>
       </c>
       <c r="E102" t="inlineStr"/>
     </row>
@@ -2703,7 +2546,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>[[1.12e+09 1.12e+09 1.12e+09]]</t>
+          <t>[[1120000000.0, 1120000000.0, 1120000000.0]]</t>
         </is>
       </c>
       <c r="E103" t="inlineStr"/>
@@ -2720,10 +2563,8 @@
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>[3.]</t>
-        </is>
+      <c r="D104" t="n">
+        <v>3</v>
       </c>
       <c r="E104" t="inlineStr"/>
     </row>
@@ -2739,10 +2580,8 @@
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>[3.55346484e+10]</t>
-        </is>
+      <c r="D105" t="n">
+        <v>35534648443.71976</v>
       </c>
       <c r="E105" t="inlineStr"/>
     </row>
@@ -2762,10 +2601,8 @@
           <t>kg/m**3</t>
         </is>
       </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>[7800.]</t>
-        </is>
+      <c r="D106" t="n">
+        <v>7800</v>
       </c>
       <c r="E106" t="inlineStr"/>
     </row>
@@ -2785,10 +2622,8 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>[0.7]</t>
-        </is>
+      <c r="D107" t="n">
+        <v>0.7</v>
       </c>
       <c r="E107" t="inlineStr"/>
     </row>
@@ -2804,10 +2639,8 @@
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>[1.07]</t>
-        </is>
+      <c r="D108" t="n">
+        <v>1.07</v>
       </c>
       <c r="E108" t="inlineStr"/>
     </row>
@@ -2829,7 +2662,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>['steel']</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="E109" t="inlineStr"/>
@@ -2875,7 +2708,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>['steel']</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="E111" t="inlineStr"/>
@@ -2896,10 +2729,8 @@
           <t>USD/min</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>[0.98]</t>
-        </is>
+      <c r="D112" t="n">
+        <v>0.98</v>
       </c>
       <c r="E112" t="inlineStr"/>
     </row>
@@ -2919,17 +2750,15 @@
           <t>USD/m**2</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>[30.]</t>
-        </is>
+      <c r="D113" t="n">
+        <v>30</v>
       </c>
       <c r="E113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>high_level_tower_props.tower_ref_axis_user</t>
+          <t>towerse.tower_mass_user</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -2939,26 +2768,18 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>[[ 0.   0.   0. ]
- [ 0.   0.  43.8]
- [ 0.   0.  87.6]]</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
-        </is>
-      </c>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>high_level_tower_props.distance_tt_hub</t>
+          <t>high_level_tower_props.tower_ref_axis_user</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -2973,19 +2794,19 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 43.8], [0.0, 0.0, 87.6]]</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vertical distance from tower top to hub center.</t>
+          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>high_level_tower_props.hub_height_user</t>
+          <t>high_level_tower_props.distance_tt_hub</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -2998,21 +2819,19 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>[90.]</t>
-        </is>
+      <c r="D116" t="n">
+        <v>0</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Height of the hub specified by the user.</t>
+          <t>Vertical distance from tower top to hub center.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>high_level_tower_props.rotor_diameter</t>
+          <t>high_level_tower_props.hub_height_user</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -3025,48 +2844,44 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D117" t="n">
+        <v>90</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Diameter of the rotor used in WISDEM. It is defined as two times the blade length plus the hub diameter.</t>
+          <t>Height of the hub specified by the user.</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>materials.rho_fiber</t>
+          <t>high_level_tower_props.rotor_diameter</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>input</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>0</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>1D array of the density of the fibers of the materials.</t>
+          <t>Diameter of the rotor used in WISDEM. It is defined as two times the blade length plus the hub diameter.</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>materials.rho</t>
+          <t>materials.rho_fiber</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -3079,21 +2894,19 @@
           <t>kg/m**3</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>[7800.]</t>
-        </is>
+      <c r="D119" t="n">
+        <v>0</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>1D array of the density of the materials. For composites, this is the density of the laminate.</t>
+          <t>1D array of the density of the fibers of the materials.</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>materials.rho_area_dry</t>
+          <t>materials.rho</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -3103,24 +2916,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>kg/m**2</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>7800</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>1D array of the dry aerial density of the composite fabrics. Non-composite materials are kept at 0.</t>
+          <t>1D array of the density of the materials. For composites, this is the density of the laminate.</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>materials.ply_t_from_yaml</t>
+          <t>materials.rho_area_dry</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -3130,24 +2941,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg/m**2</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>0</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>1D array of the ply thicknesses of the materials. Non-composite materials are kept at 0.</t>
+          <t>1D array of the dry aerial density of the composite fabrics. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>materials.fvf_from_yaml</t>
+          <t>materials.ply_t_from_yaml</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -3155,22 +2964,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr"/>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>0</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional fiber volume fraction of the composite materials. Non-composite materials are kept at 0.</t>
+          <t>1D array of the ply thicknesses of the materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>materials.fwf_from_yaml</t>
+          <t>materials.fvf_from_yaml</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -3179,21 +2990,19 @@
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D123" t="n">
+        <v>0</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional fiber weight- fraction of the composite materials. Non-composite materials are kept at 0.</t>
+          <t>1D array of the non-dimensional fiber volume fraction of the composite materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>materials.name</t>
+          <t>materials.fwf_from_yaml</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -3201,26 +3010,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>['steel']</t>
-        </is>
+      <c r="C124" t="inlineStr"/>
+      <c r="D124" t="n">
+        <v>0</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>1D array of names of materials.</t>
+          <t>1D array of the non-dimensional fiber weight- fraction of the composite materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>materials.component_id</t>
+          <t>materials.name</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -3235,19 +3038,19 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>[-1.]</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>1D array of flags to set whether a material is used in a blade: 0 - coating, 1 - sandwich filler , 2 - shell skin, 3 - shear webs, 4 - spar caps, 5 - TE/LE reinf.</t>
+          <t>1D array of names of materials.</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>tcc.hub_cost</t>
+          <t>materials.component_id</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -3257,20 +3060,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
-      </c>
-      <c r="E126" t="inlineStr"/>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>1D array of flags to set whether a material is used in a blade: 0 - coating, 1 - sandwich filler , 2 - shell skin, 3 - shear webs, 4 - spar caps, 5 - TE/LE reinf.</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>tcc.pitch_system_cost</t>
+          <t>tcc.hub_cost</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -3283,17 +3088,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D127" t="n">
+        <v>0</v>
       </c>
       <c r="E127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>tcc.spinner_cost</t>
+          <t>tcc.pitch_system_cost</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -3306,17 +3109,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D128" t="n">
+        <v>0</v>
       </c>
       <c r="E128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>tcc.lss_cost</t>
+          <t>tcc.spinner_cost</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -3329,17 +3130,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D129" t="n">
+        <v>0</v>
       </c>
       <c r="E129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>tcc.main_bearing_cost</t>
+          <t>tcc.lss_cost</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -3352,17 +3151,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D130" t="n">
+        <v>0</v>
       </c>
       <c r="E130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>tcc.gearbox_cost</t>
+          <t>tcc.main_bearing_cost</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -3375,17 +3172,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D131" t="n">
+        <v>0</v>
       </c>
       <c r="E131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>tcc.hss_cost</t>
+          <t>tcc.gearbox_cost</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -3398,17 +3193,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D132" t="n">
+        <v>0</v>
       </c>
       <c r="E132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>tcc.brake_cost</t>
+          <t>tcc.hss_cost</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -3421,17 +3214,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D133" t="n">
+        <v>0</v>
       </c>
       <c r="E133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>tcc.generator_cost</t>
+          <t>tcc.brake_cost</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -3444,17 +3235,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D134" t="n">
+        <v>0</v>
       </c>
       <c r="E134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>tcc.bedplate_cost</t>
+          <t>tcc.generator_cost</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -3467,17 +3256,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D135" t="n">
+        <v>0</v>
       </c>
       <c r="E135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>tcc.yaw_system_cost</t>
+          <t>tcc.bedplate_cost</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -3490,17 +3277,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D136" t="n">
+        <v>0</v>
       </c>
       <c r="E136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>tcc.converter_cost</t>
+          <t>tcc.yaw_system_cost</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -3513,17 +3298,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D137" t="n">
+        <v>0</v>
       </c>
       <c r="E137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>tcc.hvac_cost</t>
+          <t>tcc.converter_cost</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -3536,17 +3319,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D138" t="n">
+        <v>0</v>
       </c>
       <c r="E138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>tcc.cover_cost</t>
+          <t>tcc.hvac_cost</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -3559,17 +3340,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D139" t="n">
+        <v>0</v>
       </c>
       <c r="E139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>tcc.elec_cost</t>
+          <t>tcc.cover_cost</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -3582,17 +3361,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>[209250.]</t>
-        </is>
+      <c r="D140" t="n">
+        <v>0</v>
       </c>
       <c r="E140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>tcc.controls_cost</t>
+          <t>tcc.elec_cost</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -3605,17 +3382,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>[105750.]</t>
-        </is>
+      <c r="D141" t="n">
+        <v>209250</v>
       </c>
       <c r="E141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>tcc.platforms_cost</t>
+          <t>tcc.controls_cost</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -3628,17 +3403,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D142" t="n">
+        <v>105750</v>
       </c>
       <c r="E142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>tcc.transformer_cost</t>
+          <t>tcc.platforms_cost</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -3651,17 +3424,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D143" t="n">
+        <v>0</v>
       </c>
       <c r="E143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>tcc.blade_cost</t>
+          <t>tcc.transformer_cost</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -3674,17 +3445,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D144" t="n">
+        <v>0</v>
       </c>
       <c r="E144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>tcc.rotor_cost</t>
+          <t>tcc.blade_cost</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -3697,17 +3466,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D145" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D145" t="n">
+        <v>0</v>
       </c>
       <c r="E145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>tcc.rotor_mass_tcc</t>
+          <t>tcc.rotor_cost</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -3717,20 +3484,18 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D146" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>0</v>
       </c>
       <c r="E146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>tcc.nacelle_cost</t>
+          <t>tcc.rotor_mass_tcc</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -3740,20 +3505,18 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D147" t="inlineStr">
-        <is>
-          <t>[315000.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>0</v>
       </c>
       <c r="E147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>tcc.nacelle_mass_tcc</t>
+          <t>tcc.nacelle_cost</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -3763,20 +3526,18 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D148" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>315000</v>
       </c>
       <c r="E148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>tcc.tower_cost</t>
+          <t>tcc.nacelle_mass_tcc</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -3786,66 +3547,60 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D149" t="inlineStr">
-        <is>
-          <t>[781256.20935988]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>tcc.tower_mass</t>
+          <t>tcc.tower_cost</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>[264486.60964614]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>781256.2093598775</v>
       </c>
       <c r="E150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>tcc.turbine_cost</t>
+          <t>tcc.tower_mass</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>[1096256.20935988]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>264486.6096461398</v>
       </c>
       <c r="E151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>tcc.turbine_cost_kW</t>
+          <t>tcc.turbine_cost</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -3855,20 +3610,18 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>USD/kW</t>
-        </is>
-      </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>[219.25124187]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1096256.209359878</v>
       </c>
       <c r="E152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>tcc.turbine_mass_tcc</t>
+          <t>tcc.turbine_cost_kW</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -3878,20 +3631,18 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D153" t="inlineStr">
-        <is>
-          <t>[264486.60964614]</t>
-        </is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>219.2512418719755</v>
       </c>
       <c r="E153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>tcc.hub_system_cost</t>
+          <t>tcc.turbine_mass_tcc</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -3901,20 +3652,18 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>264486.6096461398</v>
       </c>
       <c r="E154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>tcc.hub_system_mass_tcc</t>
+          <t>tcc.hub_system_cost</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -3924,20 +3673,18 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>0</v>
       </c>
       <c r="E155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>tcc.tower_parts_cost</t>
+          <t>tcc.hub_system_mass_tcc</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -3947,25 +3694,23 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>[781256.20935988]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>0</v>
       </c>
       <c r="E156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>tcc.tower_cost_external</t>
+          <t>tcc.tower_parts_cost</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -3973,17 +3718,15 @@
           <t>USD</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>[781256.20935988]</t>
-        </is>
+      <c r="D157" t="n">
+        <v>781256.2093598775</v>
       </c>
       <c r="E157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_Px</t>
+          <t>tcc.tower_cost_external</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -3993,21 +3736,18 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>[  0.         143.91455247 182.00745621 200.40117732 207.58001213
- 207.0892654  200.80448402]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>781256.2093598775</v>
       </c>
       <c r="E158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_Py</t>
+          <t>towerse.env1.distLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -4022,7 +3762,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 143.91455246949263, 182.00745620907807, 200.4011773198595, 207.5800121260355, 207.08926540113484, 200.80448402334167]</t>
         </is>
       </c>
       <c r="E159" t="inlineStr"/>
@@ -4030,7 +3770,7 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_Pz</t>
+          <t>towerse.env1.distLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -4045,7 +3785,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E160" t="inlineStr"/>
@@ -4053,7 +3793,7 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_qdyn</t>
+          <t>towerse.env1.distLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -4063,13 +3803,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E161" t="inlineStr"/>
@@ -4077,7 +3816,7 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_z</t>
+          <t>towerse.env1.distLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -4087,12 +3826,12 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E162" t="inlineStr"/>
@@ -4100,7 +3839,7 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>towerse.env1.distLoads.windLoads_beta</t>
+          <t>towerse.env1.distLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -4110,12 +3849,12 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E163" t="inlineStr"/>
@@ -4123,35 +3862,33 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>towerse.z_global</t>
+          <t>towerse.env1.distLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>0</v>
       </c>
       <c r="E164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>towerse.wind_reference_height</t>
+          <t>towerse.z_global</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4161,7 +3898,7 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E165" t="inlineStr"/>
@@ -4169,7 +3906,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.U</t>
+          <t>towerse.wind_reference_height</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -4179,36 +3916,33 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>[ 0.          8.20235752  9.42203459 10.21793054 10.82307563 11.31703596
- 11.73732   ]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>90</v>
       </c>
       <c r="E166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>towerse.outer_diameter_full</t>
+          <t>towerse.env1.windLoads.U</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>[6.    5.645 5.29  4.935 4.58  4.225 3.87 ]</t>
+          <t>[0.0, 8.202357517700033, 9.422034587679592, 10.217930537586865, 10.823075631592713, 11.317035961080117, 11.73732]</t>
         </is>
       </c>
       <c r="E167" t="inlineStr"/>
@@ -4216,23 +3950,22 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_Px</t>
+          <t>towerse.outer_diameter_full</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>[   0.         6506.04721914 8326.99081083 9189.92845355 9486.83534284
- 9404.47282605 9059.01871719]</t>
+          <t>[6.0, 5.645, 5.29, 4.935, 4.58, 4.225, 3.87]</t>
         </is>
       </c>
       <c r="E168" t="inlineStr"/>
@@ -4240,7 +3973,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_Py</t>
+          <t>towerse.env2.distLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -4255,7 +3988,7 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 6506.04721914341, 8326.990810832196, 9189.928453553153, 9486.835342838347, 9404.472826054965, 9059.018717186304]</t>
         </is>
       </c>
       <c r="E169" t="inlineStr"/>
@@ -4263,7 +3996,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_Pz</t>
+          <t>towerse.env2.distLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -4278,7 +4011,7 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E170" t="inlineStr"/>
@@ -4286,7 +4019,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_qdyn</t>
+          <t>towerse.env2.distLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -4296,13 +4029,12 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E171" t="inlineStr"/>
@@ -4310,7 +4042,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_z</t>
+          <t>towerse.env2.distLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -4320,12 +4052,12 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E172" t="inlineStr"/>
@@ -4333,7 +4065,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>towerse.env2.distLoads.windLoads_beta</t>
+          <t>towerse.env2.distLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -4343,12 +4075,12 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E173" t="inlineStr"/>
@@ -4356,7 +4088,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.U</t>
+          <t>towerse.env2.distLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -4366,36 +4098,33 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>[ 0.         48.91789831 56.19190932 60.93853943 64.5475538  67.49347528
- 70.        ]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>0</v>
       </c>
       <c r="E174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>towerse.joint1</t>
+          <t>towerse.env2.windLoads.U</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[0.0, 48.91789831401054, 56.19190932321615, 60.93853943072869, 64.54755380372094, 67.4934752801839, 70.0]</t>
         </is>
       </c>
       <c r="E175" t="inlineStr"/>
@@ -4403,7 +4132,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>towerse.joint2</t>
+          <t>towerse.joint1</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -4418,7 +4147,7 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>[ 0.  0. 90.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E176" t="inlineStr"/>
@@ -4426,7 +4155,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>towerse.s_full</t>
+          <t>towerse.joint2</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -4441,8 +4170,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>[0.         0.16666667 0.33333333 0.5        0.66666667 0.83333333
- 1.        ]</t>
+          <t>[0.0, 0.0, 90.0]</t>
         </is>
       </c>
       <c r="E177" t="inlineStr"/>
@@ -4450,23 +4178,22 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Px_global</t>
+          <t>towerse.s_full</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>[  0.         143.91455247 182.00745621 200.40117732 207.58001213
- 207.0892654  200.80448402]</t>
+          <t>[0.0, 0.16666666666666666, 0.3333333333333333, 0.5, 0.6666666666666666, 0.8333333333333333, 1.0]</t>
         </is>
       </c>
       <c r="E178" t="inlineStr"/>
@@ -4474,7 +4201,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Py_global</t>
+          <t>towerse.g2e1.Px_global</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -4489,7 +4216,7 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 143.91455246949263, 182.00745620907807, 200.4011773198595, 207.5800121260355, 207.08926540113484, 200.80448402334167]</t>
         </is>
       </c>
       <c r="E179" t="inlineStr"/>
@@ -4497,7 +4224,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Pz_global</t>
+          <t>towerse.g2e1.Py_global</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -4512,7 +4239,7 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E180" t="inlineStr"/>
@@ -4520,7 +4247,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>towerse.g2e1.qdyn_global</t>
+          <t>towerse.g2e1.Pz_global</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -4530,13 +4257,12 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E181" t="inlineStr"/>
@@ -4544,7 +4270,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Px_global</t>
+          <t>towerse.g2e1.qdyn_global</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -4554,13 +4280,12 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>[   0.         6506.04721914 8326.99081083 9189.92845355 9486.83534284
- 9404.47282605 9059.01871719]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E182" t="inlineStr"/>
@@ -4568,7 +4293,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Py_global</t>
+          <t>towerse.g2e2.Px_global</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -4583,7 +4308,7 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 6506.04721914341, 8326.990810832196, 9189.928453553153, 9486.835342838347, 9404.472826054965, 9059.018717186304]</t>
         </is>
       </c>
       <c r="E183" t="inlineStr"/>
@@ -4591,7 +4316,7 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Pz_global</t>
+          <t>towerse.g2e2.Py_global</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -4606,7 +4331,7 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E184" t="inlineStr"/>
@@ -4614,7 +4339,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>towerse.g2e2.qdyn_global</t>
+          <t>towerse.g2e2.Pz_global</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -4624,13 +4349,12 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E185" t="inlineStr"/>
@@ -4638,7 +4362,7 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>towerse.lc1:Px</t>
+          <t>towerse.g2e2.qdyn_global</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -4648,12 +4372,12 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E186" t="inlineStr"/>
@@ -4661,7 +4385,7 @@
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>towerse.lc1:Py</t>
+          <t>towerse.lc1:Px</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -4676,7 +4400,7 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E187" t="inlineStr"/>
@@ -4684,7 +4408,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>towerse.lc1:Pz</t>
+          <t>towerse.lc1:Py</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -4699,8 +4423,7 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>[   0.         -143.91455247 -182.00745621 -200.40117732 -207.58001213
- -207.0892654  -200.80448402]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E188" t="inlineStr"/>
@@ -4708,7 +4431,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>towerse.lc1:qdyn</t>
+          <t>towerse.lc1:Pz</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -4718,13 +4441,12 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, -143.91455246949263, -182.00745620907807, -200.4011773198595, -207.5800121260355, -207.08926540113484, -200.80448402334167]</t>
         </is>
       </c>
       <c r="E189" t="inlineStr"/>
@@ -4732,7 +4454,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>towerse.lc2:Px</t>
+          <t>towerse.lc1:qdyn</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -4742,12 +4464,12 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E190" t="inlineStr"/>
@@ -4755,7 +4477,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>towerse.lc2:Py</t>
+          <t>towerse.lc2:Px</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -4770,7 +4492,7 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E191" t="inlineStr"/>
@@ -4778,7 +4500,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>towerse.lc2:Pz</t>
+          <t>towerse.lc2:Py</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -4793,8 +4515,7 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>[    0.         -6506.04721914 -8326.99081083 -9189.92845355
- -9486.83534284 -9404.47282605 -9059.01871719]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E192" t="inlineStr"/>
@@ -4802,7 +4523,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>towerse.lc2:qdyn</t>
+          <t>towerse.lc2:Pz</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -4812,13 +4533,12 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, -6506.04721914341, -8326.990810832196, -9189.928453553153, -9486.835342838347, -9404.472826054965, -9059.018717186304]</t>
         </is>
       </c>
       <c r="E193" t="inlineStr"/>
@@ -4826,22 +4546,22 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>towerse.z_full</t>
+          <t>towerse.lc2:qdyn</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E194" t="inlineStr"/>
@@ -4849,7 +4569,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>towerse.t_full</t>
+          <t>towerse.z_full</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -4864,7 +4584,7 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>[0.0246 0.0246 0.0246 0.0206 0.0206 0.0206]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E195" t="inlineStr"/>
@@ -4872,12 +4592,12 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>towerse.tower_height</t>
+          <t>towerse.t_full</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -4887,7 +4607,7 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.0246, 0.0246, 0.0246, 0.0206, 0.0206, 0.0206]</t>
         </is>
       </c>
       <c r="E196" t="inlineStr"/>
@@ -4895,30 +4615,28 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>towerse.E_full</t>
+          <t>towerse.tower_height</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D197" t="inlineStr">
-        <is>
-          <t>[2.e+11 2.e+11 2.e+11 2.e+11 2.e+11 2.e+11]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>90</v>
       </c>
       <c r="E197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>towerse.G_full</t>
+          <t>towerse.E_full</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -4933,7 +4651,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>[7.93e+10 7.93e+10 7.93e+10 7.93e+10 7.93e+10 7.93e+10]</t>
+          <t>[200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0]</t>
         </is>
       </c>
       <c r="E198" t="inlineStr"/>
@@ -4941,7 +4659,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>towerse.rho_full</t>
+          <t>towerse.G_full</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -4951,12 +4669,12 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>[7800. 7800. 7800. 7800. 7800. 7800.]</t>
+          <t>[79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0]</t>
         </is>
       </c>
       <c r="E199" t="inlineStr"/>
@@ -4964,7 +4682,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>towerse.sigma_y_full</t>
+          <t>towerse.rho_full</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -4974,12 +4692,12 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>[3.45e+08 3.45e+08 3.45e+08 3.45e+08 3.45e+08 3.45e+08]</t>
+          <t>[7800.0, 7800.0, 7800.0, 7800.0, 7800.0, 7800.0]</t>
         </is>
       </c>
       <c r="E200" t="inlineStr"/>
@@ -4987,7 +4705,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>towerse.section_A</t>
+          <t>towerse.sigma_y_full</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -4997,12 +4715,12 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>m**2</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>[0.47944576 0.45008974 0.42073372 0.32801604 0.30343336 0.27885068]</t>
+          <t>[345000000.0, 345000000.0, 345000000.0, 345000000.0, 345000000.0, 345000000.0]</t>
         </is>
       </c>
       <c r="E201" t="inlineStr"/>
@@ -5010,7 +4728,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>towerse.section_Asx</t>
+          <t>towerse.section_A</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -5025,7 +4743,7 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>[0.27258364 0.2559255  0.23926742 0.18649883 0.17254935 0.15859996]</t>
+          <t>[0.47944575529734645, 0.45008973964847976, 0.420733723999616, 0.32801604452748134, 0.30343336475648036, 0.2788506849854764]</t>
         </is>
       </c>
       <c r="E202" t="inlineStr"/>
@@ -5033,7 +4751,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>towerse.section_Asy</t>
+          <t>towerse.section_Asx</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -5048,7 +4766,7 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>[0.27258364 0.2559255  0.23926742 0.18649883 0.17254935 0.15859996]</t>
+          <t>[0.2725836432454477, 0.25592549681810994, 0.23926742226592926, 0.18649882798900633, 0.17254935179552292, 0.1585999565378346]</t>
         </is>
       </c>
       <c r="E203" t="inlineStr"/>
@@ -5056,7 +4774,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>towerse.section_Ixx</t>
+          <t>towerse.section_Asy</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -5066,12 +4784,12 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>[2.01464602 1.66678164 1.36145918 0.92002949 0.72829591 0.56524247]</t>
+          <t>[0.2725836432454477, 0.25592549681810994, 0.23926742226592926, 0.18649882798900633, 0.17254935179552292, 0.1585999565378346]</t>
         </is>
       </c>
       <c r="E204" t="inlineStr"/>
@@ -5079,7 +4797,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>towerse.section_Iyy</t>
+          <t>towerse.section_Ixx</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -5094,7 +4812,7 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>[2.01464602 1.66678164 1.36145918 0.92002949 0.72829591 0.56524247]</t>
+          <t>[2.0146460206690864, 1.6667816390360255, 1.3614591769823567, 0.9200294869539895, 0.72829590601679, 0.5652424674246717]</t>
         </is>
       </c>
       <c r="E205" t="inlineStr"/>
@@ -5102,7 +4820,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>towerse.section_J0</t>
+          <t>towerse.section_Iyy</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -5117,7 +4835,7 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>[4.02929204 3.33356328 2.72291835 1.84005897 1.45659181 1.13048493]</t>
+          <t>[2.0146460206690864, 1.6667816390360255, 1.3614591769823567, 0.9200294869539895, 0.72829590601679, 0.5652424674246717]</t>
         </is>
       </c>
       <c r="E206" t="inlineStr"/>
@@ -5125,7 +4843,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>towerse.section_rho</t>
+          <t>towerse.section_J0</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -5135,12 +4853,12 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>[7800. 7800. 7800. 7800. 7800. 7800.]</t>
+          <t>[4.029292041338173, 3.333563278072051, 2.7229183539647135, 1.840058973907979, 1.45659181203358, 1.1304849348493433]</t>
         </is>
       </c>
       <c r="E207" t="inlineStr"/>
@@ -5148,7 +4866,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>towerse.section_E</t>
+          <t>towerse.section_rho</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -5158,12 +4876,12 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>[2.e+11 2.e+11 2.e+11 2.e+11 2.e+11 2.e+11]</t>
+          <t>[7800.0, 7800.0, 7800.0, 7800.0, 7800.0, 7800.0]</t>
         </is>
       </c>
       <c r="E208" t="inlineStr"/>
@@ -5171,7 +4889,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>towerse.section_G</t>
+          <t>towerse.section_E</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -5186,7 +4904,7 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>[7.93e+10 7.93e+10 7.93e+10 7.93e+10 7.93e+10 7.93e+10]</t>
+          <t>[200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0, 200000000000.0]</t>
         </is>
       </c>
       <c r="E209" t="inlineStr"/>
@@ -5194,7 +4912,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>towerse.section_L</t>
+          <t>towerse.section_G</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -5204,12 +4922,12 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>[15. 15. 15. 15. 15. 15.]</t>
+          <t>[79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0, 79300000000.0]</t>
         </is>
       </c>
       <c r="E210" t="inlineStr"/>
@@ -5217,27 +4935,22 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Fz</t>
+          <t>towerse.section_L</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>[[-4972076.27502653 -5582894.23697993]
- [-4453250.08472071 -4956352.69969627]
- [-3967685.84805059 -4343564.7134186 ]
- [-3588310.46952875 -3828543.62156728]
- [-3237090.13374174 -3340134.23535901]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[15.0, 15.0, 15.0, 15.0, 15.0, 15.0]</t>
         </is>
       </c>
       <c r="E211" t="inlineStr"/>
@@ -5245,7 +4958,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Vx</t>
+          <t>towerse.post.cylinder_Fz</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -5260,12 +4973,7 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>[[1285330.91836013  930644.45135909]
- [1286335.79837818  931569.96328973]
- [1287177.39400341  932394.96674691]
- [1287388.29107961  932766.5855324 ]
- [1287799.88838851  933233.69954021]
- [1287882.2630758   933357.37249868]]</t>
+          <t>[[-4972076.275026535, -5582894.23697993], [-4453250.0847207075, -4956352.6996962745], [-3967685.848050595, -4343564.713418597], [-3588310.469528746, -3828543.6215672847], [-3237090.133741738, -3340134.2353590126], [-2914124.8440051214, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E212" t="inlineStr"/>
@@ -5273,7 +4981,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Vy</t>
+          <t>towerse.post.cylinder_Vx</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -5288,12 +4996,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>[[ -21.53975112    9.72450757]
- [ -65.0203353    33.31598827]
- [-111.59204184   59.9744945 ]
- [-140.89014776   81.62307871]
- [-196.86787369  116.9890197 ]
- [-257.90347891  156.09517639]]</t>
+          <t>[[1285330.9183601253, 930644.4513590932], [1286335.798378177, 931569.9632897303], [1287177.3940034062, 932394.9667469114], [1287388.2910796106, 932766.5855324045], [1287799.8883885145, 933233.6995402128], [1287882.2630757987, 933357.3724986762]]</t>
         </is>
       </c>
       <c r="E213" t="inlineStr"/>
@@ -5301,7 +5004,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Mxx</t>
+          <t>towerse.post.cylinder_Vy</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -5311,17 +5014,12 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>[[ 4195250.06133678 -1789318.89041207]
- [ 4176562.06504651 -1780372.13665228]
- [ 4145867.27608201 -1765806.84698749]
- [ 4101676.17962577 -1745191.41611634]
- [ 4041357.37979785 -1717780.08550768]
- [ 3963839.89414827 -1683733.94301481]]</t>
+          <t>[[-21.539751116884872, 9.724507568287663], [-65.02033529803157, 33.315988269168884], [-111.59204184450209, 59.974494497524574], [-140.89014775771648, 81.62307870970108], [-196.86787368822843, 116.98901969846338], [-257.9034789055586, 156.09517639130354]]</t>
         </is>
       </c>
       <c r="E214" t="inlineStr"/>
@@ -5329,7 +5027,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Myy</t>
+          <t>towerse.post.cylinder_Mxx</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -5344,12 +5042,7 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>[[97913806.02257442 70191372.50888553]
- [78185487.65802771 55870357.34363329]
- [58245379.91674052 41384206.24031743]
- [38145412.98059477 26782966.91670732]
- [17938650.49692315 12119212.35812531]
- [-2274931.50226486 -2522330.20559959]]</t>
+          <t>[[4195250.061336778, -1789318.8904120699], [4176562.065046508, -1780372.1366522796], [4145867.276082013, -1765806.846987487], [4101676.179625774, -1745191.4161163396], [4041357.379797846, -1717780.085507684], [3963839.894148268, -1683733.943014809]]</t>
         </is>
       </c>
       <c r="E215" t="inlineStr"/>
@@ -5357,7 +5050,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>towerse.post.cylinder_Mzz</t>
+          <t>towerse.post.cylinder_Myy</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -5372,12 +5065,7 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>[[-346832.06676985  147325.92244633]
- [-346829.99694222  147325.01454011]
- [-346827.97443409  147323.85565154]
- [-346834.58628055  147326.57159686]
- [-346833.40382261  147325.41116305]
- [-346832.45455505  147324.22347456]]</t>
+          <t>[[97913806.02257442, 70191372.50888553], [78185487.65802771, 55870357.34363329], [58245379.91674052, 41384206.240317434], [38145412.98059477, 26782966.916707322], [17938650.49692315, 12119212.358125314], [-2274931.5022648573, -2522330.205599591]]</t>
         </is>
       </c>
       <c r="E216" t="inlineStr"/>
@@ -5385,28 +5073,22 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>towerse.qdyn</t>
+          <t>towerse.post.cylinder_Mzz</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>[[   0.            0.        ]
- [  41.20818467 1465.68847497]
- [  54.37452566 1933.98753745]
- [  63.94873899 2274.52217262]
- [  71.74761675 2551.911855  ]
- [  78.44612305 2790.16363831]
- [  84.38086698 3001.25      ]]</t>
+          <t>[[-346832.066769847, 147325.92244633313], [-346829.9969422248, 147325.01454011156], [-346827.97443408554, 147323.85565153536], [-346834.58628055296, 147326.57159685603], [-346833.4038226075, 147325.4111630495], [-346832.45455504936, 147324.22347455847]]</t>
         </is>
       </c>
       <c r="E217" t="inlineStr"/>
@@ -5414,7 +5096,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>towerse.nodes_xyz</t>
+          <t>towerse.qdyn</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -5424,18 +5106,12 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>[[ 0.  0.  0.]
- [ 0.  0. 15.]
- [ 0.  0. 30.]
- [ 0.  0. 45.]
- [ 0.  0. 60.]
- [ 0.  0. 75.]
- [ 0.  0. 90.]]</t>
+          <t>[[0.0, 0.0], [41.208184669504284, 1465.688474969174], [54.37452566000121, 1933.9875374504848], [63.948738988457, 2274.5221726196664], [71.74761675289531, 2551.9118550021035], [78.44612305343311, 2790.1636383055375], [84.38086697922002, 3001.25]]</t>
         </is>
       </c>
       <c r="E218" t="inlineStr"/>
@@ -5443,7 +5119,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>towerse.Px</t>
+          <t>towerse.nodes_xyz</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -5453,18 +5129,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>[[0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]]</t>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 15.0], [0.0, 0.0, 30.0], [0.0, 0.0, 45.0], [0.0, 0.0, 60.0], [0.0, 0.0, 75.0], [0.0, 0.0, 90.0]]</t>
         </is>
       </c>
       <c r="E219" t="inlineStr"/>
@@ -5472,7 +5142,7 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>towerse.Py</t>
+          <t>towerse.Px</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -5487,13 +5157,7 @@
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>[[0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]
- [0. 0.]]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E220" t="inlineStr"/>
@@ -5501,7 +5165,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>towerse.Pz</t>
+          <t>towerse.Py</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -5516,13 +5180,7 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>[[    0.             0.        ]
- [ -143.91455247 -6506.04721914]
- [ -182.00745621 -8326.99081083]
- [ -200.40117732 -9189.92845355]
- [ -207.58001213 -9486.83534284]
- [ -207.0892654  -9404.47282605]
- [ -200.80448402 -9059.01871719]]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E221" t="inlineStr"/>
@@ -5530,7 +5188,7 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>towerse.tower_mass</t>
+          <t>towerse.Pz</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -5540,12 +5198,12 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>[264486.60964614]</t>
+          <t>[[0.0, 0.0], [-143.91455246949263, -6506.04721914341], [-182.00745620907807, -8326.990810832196], [-200.4011773198595, -9189.928453553153], [-207.5800121260355, -9486.835342838347], [-207.08926540113484, -9404.472826054965], [-200.80448402334167, -9059.018717186304]]</t>
         </is>
       </c>
       <c r="E222" t="inlineStr"/>
@@ -5553,7 +5211,7 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>towerse.tower_center_of_mass</t>
+          <t>towerse.tower_mass</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -5563,20 +5221,18 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D223" t="inlineStr">
-        <is>
-          <t>[39.81558198]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D223" t="n">
+        <v>264486.6096461398</v>
       </c>
       <c r="E223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>towerse.tower_I_base</t>
+          <t>towerse.tower_center_of_mass</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -5586,36 +5242,33 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
-        </is>
-      </c>
-      <c r="D224" t="inlineStr">
-        <is>
-          <t>[5.92405408e+08 5.92405408e+08 1.70009364e+06 0.00000000e+00
- 0.00000000e+00 0.00000000e+00]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D224" t="n">
+        <v>39.81558198321137</v>
       </c>
       <c r="E224" t="inlineStr"/>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>towerse.member.gc.d</t>
+          <t>towerse.tower_I_base</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg*m**2</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>[6.    4.935 3.87 ]</t>
+          <t>[592405408.0040048, 592405408.0040048, 1700093.6444286963, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E225" t="inlineStr"/>
@@ -5623,7 +5276,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>towerse.member.gc.t</t>
+          <t>towerse.member.gc.d</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -5638,7 +5291,7 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>[0.0246 0.0206]</t>
+          <t>[6.0, 4.935, 3.87]</t>
         </is>
       </c>
       <c r="E226" t="inlineStr"/>
@@ -5646,18 +5299,22 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>towerse.member.s</t>
+          <t>towerse.member.gc.t</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr"/>
+          <t>intermediate</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>[0.  0.5 1. ]</t>
+          <t>[0.0246, 0.0206]</t>
         </is>
       </c>
       <c r="E227" t="inlineStr"/>
@@ -5665,7 +5322,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>towerse.member.height</t>
+          <t>towerse.member.s</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -5673,14 +5330,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C228" t="inlineStr"/>
       <c r="D228" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.0, 0.5, 1.0]</t>
         </is>
       </c>
       <c r="E228" t="inlineStr"/>
@@ -5688,7 +5341,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>towerse.tower_outer_diameter</t>
+          <t>towerse.member.height</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -5701,17 +5354,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D229" t="inlineStr">
-        <is>
-          <t>[6.    4.935 3.87 ]</t>
-        </is>
+      <c r="D229" t="n">
+        <v>90</v>
       </c>
       <c r="E229" t="inlineStr"/>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>towerse.tower_wall_thickness</t>
+          <t>towerse.tower_outer_diameter</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -5726,7 +5377,7 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>[0.0246 0.0206]</t>
+          <t>[6.0, 4.935, 3.87]</t>
         </is>
       </c>
       <c r="E230" t="inlineStr"/>
@@ -5734,7 +5385,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>towerse.member.E</t>
+          <t>towerse.tower_wall_thickness</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -5744,12 +5395,12 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>[2.e+11 2.e+11]</t>
+          <t>[0.0246, 0.0206]</t>
         </is>
       </c>
       <c r="E231" t="inlineStr"/>
@@ -5757,7 +5408,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>towerse.member.G</t>
+          <t>towerse.member.E</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -5772,7 +5423,7 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>[7.93e+10 7.93e+10]</t>
+          <t>[200000000000.0, 200000000000.0]</t>
         </is>
       </c>
       <c r="E232" t="inlineStr"/>
@@ -5780,7 +5431,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>towerse.member.sigma_y</t>
+          <t>towerse.member.G</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -5795,7 +5446,7 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>[3.45e+08 3.45e+08]</t>
+          <t>[79300000000.0, 79300000000.0]</t>
         </is>
       </c>
       <c r="E233" t="inlineStr"/>
@@ -5803,7 +5454,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>towerse.member.rho</t>
+          <t>towerse.member.sigma_y</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -5813,12 +5464,12 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>[7800. 7800.]</t>
+          <t>[345000000.0, 345000000.0]</t>
         </is>
       </c>
       <c r="E234" t="inlineStr"/>
@@ -5826,7 +5477,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>towerse.member.unit_cost</t>
+          <t>towerse.member.rho</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -5836,12 +5487,12 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>[0.7 0.7]</t>
+          <t>[7800.0, 7800.0]</t>
         </is>
       </c>
       <c r="E235" t="inlineStr"/>
@@ -5849,7 +5500,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>towerse.member.outfitting_factor</t>
+          <t>towerse.member.unit_cost</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -5857,10 +5508,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C236" t="inlineStr"/>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>[1.07 1.07]</t>
+          <t>[0.7000000000000001, 0.7]</t>
         </is>
       </c>
       <c r="E236" t="inlineStr"/>
@@ -5868,18 +5523,18 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>towerse.tower_s</t>
+          <t>towerse.member.outfitting_factor</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
-          <t>[0.  0.5 1. ]</t>
+          <t>[1.07, 1.07]</t>
         </is>
       </c>
       <c r="E237" t="inlineStr"/>
@@ -5887,18 +5542,18 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>towerse.outfitting_full</t>
+          <t>towerse.tower_s</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C238" t="inlineStr"/>
       <c r="D238" t="inlineStr">
         <is>
-          <t>[1.07 1.07 1.07 1.07 1.07 1.07]</t>
+          <t>[0.0, 0.5, 1.0]</t>
         </is>
       </c>
       <c r="E238" t="inlineStr"/>
@@ -5906,7 +5561,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>towerse.member.unit_cost_full</t>
+          <t>towerse.outfitting_full</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -5914,14 +5569,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C239" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
+      <c r="C239" t="inlineStr"/>
       <c r="D239" t="inlineStr">
         <is>
-          <t>[0.7 0.7 0.7 0.7 0.7 0.7]</t>
+          <t>[1.07, 1.07, 1.07, 1.07, 1.07, 1.07]</t>
         </is>
       </c>
       <c r="E239" t="inlineStr"/>
@@ -5929,22 +5580,22 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>towerse.hub_height</t>
+          <t>towerse.member.unit_cost_full</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>output</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.7000000000000001, 0.7000000000000001, 0.7000000000000001, 0.7, 0.7, 0.7]</t>
         </is>
       </c>
       <c r="E240" t="inlineStr"/>
@@ -5952,7 +5603,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>towerse.foundation_height</t>
+          <t>towerse.hub_height</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -5965,17 +5616,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D241" t="n">
+        <v>90</v>
       </c>
       <c r="E241" t="inlineStr"/>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>tower_grid.ref_axis</t>
+          <t>towerse.foundation_height</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -5988,47 +5637,42 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D242" t="inlineStr">
-        <is>
-          <t>[[ 0.  0.  0.]
- [ 0.  0. 45.]
- [ 0.  0. 90.]]</t>
-        </is>
-      </c>
-      <c r="E242" t="inlineStr">
-        <is>
-          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
-        </is>
-      </c>
+      <c r="D242" t="n">
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr"/>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>towerse.env1.Px</t>
+          <t>tower_grid.ref_axis</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>output</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>[  0.         143.91455247 182.00745621 200.40117732 207.58001213
- 207.0892654  200.80448402]</t>
-        </is>
-      </c>
-      <c r="E243" t="inlineStr"/>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 45.0], [0.0, 0.0, 90.0]]</t>
+        </is>
+      </c>
+      <c r="E243" t="inlineStr">
+        <is>
+          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>towerse.env1.Py</t>
+          <t>towerse.env1.Px</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -6043,7 +5687,7 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 143.91455246949263, 182.00745620907807, 200.4011773198595, 207.5800121260355, 207.08926540113484, 200.80448402334167]</t>
         </is>
       </c>
       <c r="E244" t="inlineStr"/>
@@ -6051,7 +5695,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>towerse.env1.Pz</t>
+          <t>towerse.env1.Py</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -6066,7 +5710,7 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E245" t="inlineStr"/>
@@ -6074,7 +5718,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>towerse.env1.qdyn</t>
+          <t>towerse.env1.Pz</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -6084,13 +5728,12 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E246" t="inlineStr"/>
@@ -6098,7 +5741,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>towerse.env1.wind.U</t>
+          <t>towerse.env1.qdyn</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -6108,13 +5751,12 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>[ 0.          8.20235752  9.42203459 10.21793054 10.82307563 11.31703596
- 11.73732   ]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E247" t="inlineStr"/>
@@ -6122,7 +5764,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_Px</t>
+          <t>towerse.env1.wind.U</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -6132,13 +5774,12 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>[  0.         143.91455247 182.00745621 200.40117732 207.58001213
- 207.0892654  200.80448402]</t>
+          <t>[0.0, 8.202357517700033, 9.422034587679592, 10.217930537586865, 10.823075631592713, 11.317035961080117, 11.73732]</t>
         </is>
       </c>
       <c r="E248" t="inlineStr"/>
@@ -6146,7 +5787,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_Py</t>
+          <t>towerse.env1.windLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -6161,7 +5802,7 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 143.91455246949263, 182.00745620907807, 200.4011773198595, 207.5800121260355, 207.08926540113484, 200.80448402334167]</t>
         </is>
       </c>
       <c r="E249" t="inlineStr"/>
@@ -6169,7 +5810,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_Pz</t>
+          <t>towerse.env1.windLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -6184,7 +5825,7 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E250" t="inlineStr"/>
@@ -6192,7 +5833,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_qdyn</t>
+          <t>towerse.env1.windLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -6202,13 +5843,12 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E251" t="inlineStr"/>
@@ -6216,7 +5856,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_z</t>
+          <t>towerse.env1.windLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -6226,12 +5866,12 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E252" t="inlineStr"/>
@@ -6239,7 +5879,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>towerse.env1.windLoads.windLoads_beta</t>
+          <t>towerse.env1.windLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -6249,12 +5889,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E253" t="inlineStr"/>
@@ -6262,7 +5902,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>towerse.env2.Px</t>
+          <t>towerse.env1.windLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -6272,21 +5912,18 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>[   0.         6506.04721914 8326.99081083 9189.92845355 9486.83534284
- 9404.47282605 9059.01871719]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D254" t="n">
+        <v>0</v>
       </c>
       <c r="E254" t="inlineStr"/>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>towerse.env2.Py</t>
+          <t>towerse.env2.Px</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -6301,7 +5938,7 @@
       </c>
       <c r="D255" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 6506.04721914341, 8326.990810832196, 9189.928453553153, 9486.835342838347, 9404.472826054965, 9059.018717186304]</t>
         </is>
       </c>
       <c r="E255" t="inlineStr"/>
@@ -6309,7 +5946,7 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>towerse.env2.Pz</t>
+          <t>towerse.env2.Py</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
@@ -6324,7 +5961,7 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E256" t="inlineStr"/>
@@ -6332,7 +5969,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>towerse.env2.qdyn</t>
+          <t>towerse.env2.Pz</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -6342,13 +5979,12 @@
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E257" t="inlineStr"/>
@@ -6356,7 +5992,7 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>towerse.env2.wind.U</t>
+          <t>towerse.env2.qdyn</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
@@ -6366,13 +6002,12 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>m/s</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>[ 0.         48.91789831 56.19190932 60.93853943 64.5475538  67.49347528
- 70.        ]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E258" t="inlineStr"/>
@@ -6380,7 +6015,7 @@
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_Px</t>
+          <t>towerse.env2.wind.U</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -6390,13 +6025,12 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>m/s</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>[   0.         6506.04721914 8326.99081083 9189.92845355 9486.83534284
- 9404.47282605 9059.01871719]</t>
+          <t>[0.0, 48.91789831401054, 56.19190932321615, 60.93853943072869, 64.54755380372094, 67.4934752801839, 70.0]</t>
         </is>
       </c>
       <c r="E259" t="inlineStr"/>
@@ -6404,7 +6038,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_Py</t>
+          <t>towerse.env2.windLoads.windLoads_Px</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -6419,7 +6053,7 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 6506.04721914341, 8326.990810832196, 9189.928453553153, 9486.835342838347, 9404.472826054965, 9059.018717186304]</t>
         </is>
       </c>
       <c r="E260" t="inlineStr"/>
@@ -6427,7 +6061,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_Pz</t>
+          <t>towerse.env2.windLoads.windLoads_Py</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -6442,7 +6076,7 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E261" t="inlineStr"/>
@@ -6450,7 +6084,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_qdyn</t>
+          <t>towerse.env2.windLoads.windLoads_Pz</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -6460,13 +6094,12 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>N/m**2</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E262" t="inlineStr"/>
@@ -6474,7 +6107,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_z</t>
+          <t>towerse.env2.windLoads.windLoads_qdyn</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -6484,12 +6117,12 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N/m**2</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E263" t="inlineStr"/>
@@ -6497,7 +6130,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>towerse.env2.windLoads.windLoads_beta</t>
+          <t>towerse.env2.windLoads.windLoads_z</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -6507,12 +6140,12 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>deg</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E264" t="inlineStr"/>
@@ -6520,7 +6153,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Px</t>
+          <t>towerse.env2.windLoads.windLoads_beta</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -6530,20 +6163,18 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>N/m</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>deg</t>
+        </is>
+      </c>
+      <c r="D265" t="n">
+        <v>0</v>
       </c>
       <c r="E265" t="inlineStr"/>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Py</t>
+          <t>towerse.g2e1.Px</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -6558,7 +6189,7 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E266" t="inlineStr"/>
@@ -6566,7 +6197,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>towerse.g2e1.Pz</t>
+          <t>towerse.g2e1.Py</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -6581,8 +6212,7 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>[   0.         -143.91455247 -182.00745621 -200.40117732 -207.58001213
- -207.0892654  -200.80448402]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E267" t="inlineStr"/>
@@ -6590,7 +6220,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>towerse.g2e1.qdyn</t>
+          <t>towerse.g2e1.Pz</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -6600,13 +6230,12 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>[ 0.         41.20818467 54.37452566 63.94873899 71.74761675 78.44612305
- 84.38086698]</t>
+          <t>[0.0, -143.91455246949263, -182.00745620907807, -200.4011773198595, -207.5800121260355, -207.08926540113484, -200.80448402334167]</t>
         </is>
       </c>
       <c r="E268" t="inlineStr"/>
@@ -6614,7 +6243,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Px</t>
+          <t>towerse.g2e1.qdyn</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -6624,12 +6253,12 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>N/m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 41.208184669504284, 54.37452566000121, 63.948738988457, 71.74761675289531, 78.44612305343311, 84.38086697922002]</t>
         </is>
       </c>
       <c r="E269" t="inlineStr"/>
@@ -6637,7 +6266,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Py</t>
+          <t>towerse.g2e2.Px</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -6652,7 +6281,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E270" t="inlineStr"/>
@@ -6660,7 +6289,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>towerse.g2e2.Pz</t>
+          <t>towerse.g2e2.Py</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -6675,8 +6304,7 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>[    0.         -6506.04721914 -8326.99081083 -9189.92845355
- -9486.83534284 -9404.47282605 -9059.01871719]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E271" t="inlineStr"/>
@@ -6684,7 +6312,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>towerse.g2e2.qdyn</t>
+          <t>towerse.g2e2.Pz</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -6694,13 +6322,12 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>N/m</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>[   0.         1465.68847497 1933.98753745 2274.52217262 2551.911855
- 2790.16363831 3001.25      ]</t>
+          <t>[0.0, -6506.04721914341, -8326.990810832196, -9189.928453553153, -9486.835342838347, -9404.472826054965, -9059.018717186304]</t>
         </is>
       </c>
       <c r="E272" t="inlineStr"/>
@@ -6708,7 +6335,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>towerse.post.axial_stress</t>
+          <t>towerse.g2e2.qdyn</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -6723,12 +6350,7 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>[[1.31249001e+08 8.98180230e+07]
- [1.18523594e+08 8.06696248e+07]
- [1.00206714e+08 6.74491180e+07]
- [8.82546224e+07 5.77227969e+07]
- [4.49096636e+07 2.59882354e+07]
- [5.91254220e+06 5.18701022e+05]]</t>
+          <t>[0.0, 1465.688474969174, 1933.9875374504848, 2274.5221726196664, 2551.9118550021035, 2790.1636383055375, 3001.25]</t>
         </is>
       </c>
       <c r="E273" t="inlineStr"/>
@@ -6736,7 +6358,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>towerse.post.shear_stress</t>
+          <t>towerse.post.axial_stress</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -6751,12 +6373,7 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>[[4965956.95432832 3520607.1688945 ]
- [5310636.31820759 3760821.10806681]
- [5705258.89755748 4035180.12458355]
- [7351302.70558983 5191918.38983957]
- [7987517.61298305 5631146.17827651]
- [8741205.22629173 6148712.89680142]]</t>
+          <t>[[131249001.4635263, 89818022.98176754], [118523593.90465806, 80669624.8438066], [100206714.2880511, 67449117.98076226], [88254622.35159148, 57722796.90766907], [44909663.62784208, 25988235.434132457], [5912542.195458269, 518701.0217758175]]</t>
         </is>
       </c>
       <c r="E274" t="inlineStr"/>
@@ -6764,7 +6381,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>towerse.post.hoop_stress</t>
+          <t>towerse.post.shear_stress</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -6779,12 +6396,7 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>[[  -2428.05827129  -86360.92692097]
- [  -5287.06437045 -188049.76186991]
- [  -6118.05831509 -217606.46904335]
- [  -7800.72897465 -277455.52603691]
- [  -7987.06248128 -284083.01704035]
- [  -7957.37871556 -283027.22791374]]</t>
+          <t>[[4965956.954328318, 3520607.168894504], [5310636.318207593, 3760821.1080668066], [5705258.897557483, 4035180.12458355], [7351302.705589827, 5191918.389839569], [7987517.612983046, 5631146.178276515], [8741205.226291735, 6148712.896801421]]</t>
         </is>
       </c>
       <c r="E275" t="inlineStr"/>
@@ -6792,7 +6404,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>towerse.post.hoop_stress_euro</t>
+          <t>towerse.post.hoop_stress</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -6807,12 +6419,7 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>[[  -1578.23787634  -56134.60249863]
- [  -3436.59184079 -122232.34521544]
- [  -3976.73790481 -141444.20487818]
- [  -5070.47383352 -180346.09192399]
- [  -5191.59061283 -184653.96107623]
- [  -5172.29616512 -183967.69814393]]</t>
+          <t>[[-2428.058271293891, -86360.9269209733], [-5287.064370451883, -188049.7618699081], [-6118.05831509035, -217606.46904335284], [-7800.7289746506285, -277455.52603691217], [-7987.062481278526, -284083.0170403489], [-7957.378715564208, -283027.22791374475]]</t>
         </is>
       </c>
       <c r="E276" t="inlineStr"/>
@@ -6820,7 +6427,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>towerse.post.constr_stress</t>
+          <t>towerse.post.hoop_stress_euro</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -6828,15 +6435,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C277" t="inlineStr"/>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>[[0.66909629 0.45817146]
- [0.60475072 0.41217612]
- [0.51223527 0.34549972]
- [0.45361541 0.29787516]
- [0.23906736 0.141887  ]
- [0.08268946 0.05429381]]</t>
+          <t>[[0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0], [0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E277" t="inlineStr"/>
@@ -6844,7 +6450,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>towerse.post.constr_shell_buckling</t>
+          <t>towerse.post.constr_stress</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -6855,12 +6461,7 @@
       <c r="C278" t="inlineStr"/>
       <c r="D278" t="inlineStr">
         <is>
-          <t>[[0.66770985 0.33996079]
- [0.53427441 0.26914926]
- [0.38014963 0.18757178]
- [0.33613978 0.16118199]
- [0.10627418 0.04500569]
- [0.01993404 0.01196304]]</t>
+          <t>[[0.6690962934520785, 0.4581714600257803], [0.6047507237976859, 0.41217612489654687], [0.5122352700859173, 0.34549971581710887], [0.4536154061014502, 0.29787515710110896], [0.23906736336548393, 0.14188700156111203], [0.08268945594823299, 0.05429381225547569]]</t>
         </is>
       </c>
       <c r="E278" t="inlineStr"/>
@@ -6868,7 +6469,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>towerse.post.constr_global_buckling</t>
+          <t>towerse.post.constr_shell_buckling</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -6879,12 +6480,7 @@
       <c r="C279" t="inlineStr"/>
       <c r="D279" t="inlineStr">
         <is>
-          <t>[[0.83510456 0.66367515]
- [0.77894626 0.6228039 ]
- [0.69883621 0.56376602]
- [0.68319271 0.55657269]
- [0.49971485 0.42001658]
- [0.34163296 0.314881  ]]</t>
+          <t>[[0.12904749088631914, 0.12119136512295069], [0.12613904558004435, 0.12343200506324582], [0.1237769002456743, 0.12028045314494223], [0.1747216370791786, 0.16890434676338542], [0.17403977859102152, 0.1640418456948297], [0.1745842291431741, 0.1593900390268539]]</t>
         </is>
       </c>
       <c r="E279" t="inlineStr"/>
@@ -6892,7 +6488,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>towerse.tower.f1</t>
+          <t>towerse.post.constr_global_buckling</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -6900,14 +6496,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C280" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
+      <c r="C280" t="inlineStr"/>
       <c r="D280" t="inlineStr">
         <is>
-          <t>[0.28471966]</t>
+          <t>[[1.2511353948462127, 0.9379088509135679], [1.1741180869165224, 0.8795071383418506], [1.0484564725747512, 0.7842042240771947], [1.0248121280249896, 0.7642751011947516], [0.6452393279964446, 0.47918052276354517], [0.3033587314343217, 0.24989321852831242]]</t>
         </is>
       </c>
       <c r="E280" t="inlineStr"/>
@@ -6915,7 +6507,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>towerse.tower.f2</t>
+          <t>towerse.tower.f1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -6928,17 +6520,15 @@
           <t>Hz</t>
         </is>
       </c>
-      <c r="D281" t="inlineStr">
-        <is>
-          <t>[0.29952468]</t>
-        </is>
+      <c r="D281" t="n">
+        <v>0.2847196640143113</v>
       </c>
       <c r="E281" t="inlineStr"/>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>towerse.tower.structural_frequencies</t>
+          <t>towerse.tower.f2</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -6951,17 +6541,15 @@
           <t>Hz</t>
         </is>
       </c>
-      <c r="D282" t="inlineStr">
-        <is>
-          <t>[0.28471966 0.29952468 1.15579806 1.52584656 2.08805702 4.00096798]</t>
-        </is>
+      <c r="D282" t="n">
+        <v>0.299524680016962</v>
       </c>
       <c r="E282" t="inlineStr"/>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>towerse.tower.fore_aft_modes</t>
+          <t>towerse.tower.structural_frequencies</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -6969,15 +6557,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C283" t="inlineStr"/>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Hz</t>
+        </is>
+      </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>[[ 1.18315849e+00 -4.96363418e-01  6.74643791e-01 -3.16047134e-01
-  -4.53917248e-02]
- [-1.02872761e+02  1.41829460e+02 -1.52271029e+02  1.98134559e+02
-  -8.38202296e+01]
- [-9.87051132e+01  1.47203308e+02  2.16843544e+01 -4.84878125e+01
-  -2.06947367e+01]]</t>
+          <t>[0.2847196640143113, 0.29952468001696203, 1.155798059116858, 1.525846557174814, 2.0880570196938484, 4.000967982247543]</t>
         </is>
       </c>
       <c r="E283" t="inlineStr"/>
@@ -6985,7 +6572,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>towerse.tower.side_side_modes</t>
+          <t>towerse.tower.fore_aft_modes</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -6996,12 +6583,7 @@
       <c r="C284" t="inlineStr"/>
       <c r="D284" t="inlineStr">
         <is>
-          <t>[[ 1.12937103e+00 -4.31146245e-01  5.90053890e-01 -2.15682172e-01
-  -7.25964987e-02]
- [ 1.50251297e+01 -1.80501991e+01  2.23886204e+01 -2.69915319e+01
-   8.62798089e+00]
- [-6.93968841e+01  1.04601460e+02 -3.00838699e+01  3.72095183e+01
-  -4.13302239e+01]]</t>
+          <t>[[1.1831584852577295, -0.49636341758041225, 0.6746437907600378, -0.31604713359915265, -0.04539172483826045], [-102.87276079638585, 141.82946046731266, -152.2710291950007, 198.13455913017512, -83.82022960610195], [-98.70511321708851, 147.20330808374493, 21.68435439935639, -48.48781253780113, -20.694736728211403]]</t>
         </is>
       </c>
       <c r="E284" t="inlineStr"/>
@@ -7009,7 +6591,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>towerse.tower.torsion_modes</t>
+          <t>towerse.tower.side_side_modes</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -7020,9 +6602,7 @@
       <c r="C285" t="inlineStr"/>
       <c r="D285" t="inlineStr">
         <is>
-          <t>[[ 10.1035482  -42.41754984  81.37983221 -71.73393441  23.66810384]
- [  0.           0.           0.           0.           0.        ]
- [  0.           0.           0.           0.           0.        ]]</t>
+          <t>[[1.129371025091538, -0.43114624490944903, 0.5900538900566507, -0.21568217151507388, -0.07259649872372732], [15.02512970914049, -18.050199123751856, 22.388620391155893, -26.991531862949017, 8.627980886404254], [-69.39688411422695, 104.60145973731152, -30.083869927087132, 37.209518251032506, -41.330223947029744]]</t>
         </is>
       </c>
       <c r="E285" t="inlineStr"/>
@@ -7030,7 +6610,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>towerse.tower.fore_aft_freqs</t>
+          <t>towerse.tower.torsion_modes</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -7038,14 +6618,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C286" t="inlineStr">
-        <is>
-          <t>Hz</t>
-        </is>
-      </c>
+      <c r="C286" t="inlineStr"/>
       <c r="D286" t="inlineStr">
         <is>
-          <t>[0.29952468 2.08805702 4.65125998]</t>
+          <t>[[10.103548204277107, -42.41754984350535, 81.37983220745735, -71.73393440864022, 23.66810384041105], [0.0, 0.0, 0.0, 0.0, 0.0], [0.0, 0.0, 0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E286" t="inlineStr"/>
@@ -7053,7 +6629,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>towerse.tower.side_side_freqs</t>
+          <t>towerse.tower.fore_aft_freqs</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -7068,7 +6644,7 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>[0.28471966 1.15579806 4.00096798]</t>
+          <t>[0.29952468001696203, 2.0880570196938484, 4.651259975893211]</t>
         </is>
       </c>
       <c r="E287" t="inlineStr"/>
@@ -7076,7 +6652,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>towerse.tower.torsion_freqs</t>
+          <t>towerse.tower.side_side_freqs</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -7091,7 +6667,7 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>[7.63612364 0.         0.        ]</t>
+          <t>[0.2847196640143113, 1.155798059116858, 4.000967982247543]</t>
         </is>
       </c>
       <c r="E288" t="inlineStr"/>
@@ -7099,7 +6675,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_deflection</t>
+          <t>towerse.tower.torsion_freqs</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -7109,18 +6685,12 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Hz</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>[[0.         0.        ]
- [0.03188654 0.02288476]
- [0.12388813 0.08883587]
- [0.27422685 0.19643225]
- [0.48335244 0.3457213 ]
- [0.7445208  0.53142941]
- [1.03641681 0.73767571]]</t>
+          <t>[7.636123643488137, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E289" t="inlineStr"/>
@@ -7128,7 +6698,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>towerse.tower.top_deflection</t>
+          <t>towerse.tower.tower_deflection</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -7143,7 +6713,7 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>[1.03641681 0.73767571]</t>
+          <t>[[0.0, 0.0], [0.03188654392737557, 0.02288476163492425], [0.12388812623133455, 0.08883586955422126], [0.27422685105278727, 0.19643225188246263], [0.4833524387067909, 0.34572129930801143], [0.744520799454688, 0.5314294117193923], [1.0364168135656224, 0.7376757097287132]]</t>
         </is>
       </c>
       <c r="E290" t="inlineStr"/>
@@ -7151,7 +6721,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Fz</t>
+          <t>towerse.tower.top_deflection</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -7161,17 +6731,12 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>[[-4972076.27502653 -5582894.23697993]
- [-4453250.08472071 -4956352.69969627]
- [-3967685.84805059 -4343564.7134186 ]
- [-3588310.46952875 -3828543.62156728]
- [-3237090.13374174 -3340134.23535901]
- [-2914124.84400512 -2883106.12368949]]</t>
+          <t>[1.0364168135656224, 0.7376757097287132]</t>
         </is>
       </c>
       <c r="E291" t="inlineStr"/>
@@ -7179,7 +6744,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Vx</t>
+          <t>towerse.tower.tower_Fz</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -7194,12 +6759,7 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>[[1285330.91836013  930644.45135909]
- [1286335.79837818  931569.96328973]
- [1287177.39400341  932394.96674691]
- [1287388.29107961  932766.5855324 ]
- [1287799.88838851  933233.69954021]
- [1287882.2630758   933357.37249868]]</t>
+          <t>[[-4972076.275026535, -5582894.23697993], [-4453250.0847207075, -4956352.6996962745], [-3967685.848050595, -4343564.713418597], [-3588310.469528746, -3828543.6215672847], [-3237090.133741738, -3340134.2353590126], [-2914124.8440051214, -2883106.12368949]]</t>
         </is>
       </c>
       <c r="E292" t="inlineStr"/>
@@ -7207,7 +6767,7 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Vy</t>
+          <t>towerse.tower.tower_Vx</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
@@ -7222,12 +6782,7 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>[[ -21.53975112    9.72450757]
- [ -65.0203353    33.31598827]
- [-111.59204184   59.9744945 ]
- [-140.89014776   81.62307871]
- [-196.86787369  116.9890197 ]
- [-257.90347891  156.09517639]]</t>
+          <t>[[1285330.9183601253, 930644.4513590932], [1286335.798378177, 931569.9632897303], [1287177.3940034062, 932394.9667469114], [1287388.2910796106, 932766.5855324045], [1287799.8883885145, 933233.6995402128], [1287882.2630757987, 933357.3724986762]]</t>
         </is>
       </c>
       <c r="E293" t="inlineStr"/>
@@ -7235,7 +6790,7 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Mxx</t>
+          <t>towerse.tower.tower_Vy</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
@@ -7245,17 +6800,12 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>[[ 4195250.06133678 -1789318.89041207]
- [ 4176562.06504651 -1780372.13665228]
- [ 4145867.27608201 -1765806.84698749]
- [ 4101676.17962577 -1745191.41611634]
- [ 4041357.37979785 -1717780.08550768]
- [ 3963839.89414827 -1683733.94301481]]</t>
+          <t>[[-21.539751116884872, 9.724507568287663], [-65.02033529803157, 33.315988269168884], [-111.59204184450209, 59.974494497524574], [-140.89014775771648, 81.62307870970108], [-196.86787368822843, 116.98901969846338], [-257.9034789055586, 156.09517639130354]]</t>
         </is>
       </c>
       <c r="E294" t="inlineStr"/>
@@ -7263,7 +6813,7 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Myy</t>
+          <t>towerse.tower.tower_Mxx</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -7278,12 +6828,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>[[97913806.02257442 70191372.50888553]
- [78185487.65802771 55870357.34363329]
- [58245379.91674052 41384206.24031743]
- [38145412.98059477 26782966.91670732]
- [17938650.49692315 12119212.35812531]
- [-2274931.50226486 -2522330.20559959]]</t>
+          <t>[[4195250.061336778, -1789318.8904120699], [4176562.065046508, -1780372.1366522796], [4145867.276082013, -1765806.846987487], [4101676.179625774, -1745191.4161163396], [4041357.379797846, -1717780.085507684], [3963839.894148268, -1683733.943014809]]</t>
         </is>
       </c>
       <c r="E295" t="inlineStr"/>
@@ -7291,7 +6836,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>towerse.tower.tower_Mzz</t>
+          <t>towerse.tower.tower_Myy</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -7306,12 +6851,7 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>[[-346832.06676985  147325.92244633]
- [-346829.99694222  147325.01454011]
- [-346827.97443409  147323.85565154]
- [-346834.58628055  147326.57159686]
- [-346833.40382261  147325.41116305]
- [-346832.45455505  147324.22347456]]</t>
+          <t>[[97913806.02257442, 70191372.50888553], [78185487.65802771, 55870357.34363329], [58245379.91674052, 41384206.240317434], [38145412.98059477, 26782966.916707322], [17938650.49692315, 12119212.358125314], [-2274931.5022648573, -2522330.205599591]]</t>
         </is>
       </c>
       <c r="E296" t="inlineStr"/>
@@ -7319,7 +6859,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>towerse.tower.turbine_F</t>
+          <t>towerse.tower.tower_Mzz</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -7329,14 +6869,12 @@
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>[[ 1.28474420e+06  9.30198601e+05]
- [ 2.91038305e-09  5.82076609e-11]
- [-5.52323243e+06 -6.18128923e+06]]</t>
+          <t>[[-346832.066769847, 147325.92244633313], [-346829.9969422248, 147325.01454011156], [-346827.97443408554, 147323.85565153536], [-346834.58628055296, 147326.57159685603], [-346833.4038226075, 147325.4111630495], [-346832.45455504936, 147324.22347455847]]</t>
         </is>
       </c>
       <c r="E297" t="inlineStr"/>
@@ -7344,7 +6882,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>towerse.tower.turbine_M</t>
+          <t>towerse.tower.turbine_F</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -7354,14 +6892,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>N*m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>[[ 4.20167571e+06 -1.79238798e+06]
- [ 1.17359599e+08  8.42847367e+07]
- [-3.46781682e+05  1.47301970e+05]]</t>
+          <t>[[1284744.1962052211, 930198.6006327774], [2.9103830456733704e-09, 5.820766091346741e-11], [-5523232.426907699, -6181289.226207387]]</t>
         </is>
       </c>
       <c r="E298" t="inlineStr"/>
@@ -7369,7 +6905,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>towerse.turbine_mass</t>
+          <t>towerse.tower.turbine_M</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -7379,12 +6915,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>kg</t>
+          <t>N*m</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>[550085.40964614]</t>
+          <t>[[4201675.706759548, -1792387.9815820227], [117359599.22263148, 84284736.71474367], [-346781.68192839023, 147301.97023763997]]</t>
         </is>
       </c>
       <c r="E299" t="inlineStr"/>
@@ -7392,7 +6928,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>towerse.turbine_center_of_mass</t>
+          <t>towerse.turbine_mass</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -7402,20 +6938,18 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr">
-        <is>
-          <t>[-0.58771071  0.         66.13496524]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D300" t="n">
+        <v>550085.4096461397</v>
       </c>
       <c r="E300" t="inlineStr"/>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>towerse.turbine_I_base</t>
+          <t>towerse.turbine_center_of_mass</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -7425,13 +6959,12 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>kg*m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>[3.02068637e+09 2.92779109e+09 2.04598361e+07 0.00000000e+00
- 5.03710467e+05 0.00000000e+00]</t>
+          <t>[-0.5877107109536817, 0.0, 66.1349652377343]</t>
         </is>
       </c>
       <c r="E301" t="inlineStr"/>
@@ -7439,7 +6972,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>towerse.constr_d_to_t</t>
+          <t>towerse.turbine_I_base</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -7447,10 +6980,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C302" t="inlineStr"/>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>kg*m**2</t>
+        </is>
+      </c>
       <c r="D302" t="inlineStr">
         <is>
-          <t>[222.25609756 213.71359223]</t>
+          <t>[3020686366.004005, 2927791091.004005, 20459836.144428696, 0.0, 503710.467, 0.0]</t>
         </is>
       </c>
       <c r="E302" t="inlineStr"/>
@@ -7458,7 +6995,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>towerse.constr_taper</t>
+          <t>towerse.constr_d_to_t</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -7469,7 +7006,7 @@
       <c r="C303" t="inlineStr"/>
       <c r="D303" t="inlineStr">
         <is>
-          <t>[0.8225     0.78419453]</t>
+          <t>[222.25609756097558, 213.7135922330097]</t>
         </is>
       </c>
       <c r="E303" t="inlineStr"/>
@@ -7477,7 +7014,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>towerse.slope</t>
+          <t>towerse.constr_taper</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -7488,7 +7025,7 @@
       <c r="C304" t="inlineStr"/>
       <c r="D304" t="inlineStr">
         <is>
-          <t>[0.8225     0.78419453]</t>
+          <t>[0.8224999999999999, 0.78419452887538]</t>
         </is>
       </c>
       <c r="E304" t="inlineStr"/>
@@ -7496,7 +7033,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>towerse.thickness_slope</t>
+          <t>towerse.slope</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -7507,7 +7044,7 @@
       <c r="C305" t="inlineStr"/>
       <c r="D305" t="inlineStr">
         <is>
-          <t>[0.83739837]</t>
+          <t>[0.8224999999999999, 0.78419452887538]</t>
         </is>
       </c>
       <c r="E305" t="inlineStr"/>
@@ -7515,7 +7052,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>towerse.member.ca_usr_grid_full</t>
+          <t>towerse.thickness_slope</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -7524,17 +7061,15 @@
         </is>
       </c>
       <c r="C306" t="inlineStr"/>
-      <c r="D306" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
-        </is>
+      <c r="D306" t="n">
+        <v>0.8373983739837398</v>
       </c>
       <c r="E306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>towerse.member.cd_usr_grid_full</t>
+          <t>towerse.member.ca_usr_grid_full</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -7545,7 +7080,7 @@
       <c r="C307" t="inlineStr"/>
       <c r="D307" t="inlineStr">
         <is>
-          <t>[0. 0. 0. 0. 0. 0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E307" t="inlineStr"/>
@@ -7553,7 +7088,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>towerse.member.nu_full</t>
+          <t>towerse.member.cd_usr_grid_full</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -7564,7 +7099,7 @@
       <c r="C308" t="inlineStr"/>
       <c r="D308" t="inlineStr">
         <is>
-          <t>[0.26103405 0.26103405 0.26103405 0.26103405 0.26103405 0.26103405]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E308" t="inlineStr"/>
@@ -7572,7 +7107,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>towerse.member.nodes_r</t>
+          <t>towerse.member.nu_full</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -7580,14 +7115,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C309" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C309" t="inlineStr"/>
       <c r="D309" t="inlineStr">
         <is>
-          <t>[3.     2.8225 2.645  2.4675 2.29   2.1125 1.935 ]</t>
+          <t>[0.26103404791929385, 0.26103404791929385, 0.26103404791929385, 0.26103404791929385, 0.26103404791929385, 0.26103404791929385]</t>
         </is>
       </c>
       <c r="E309" t="inlineStr"/>
@@ -7595,7 +7126,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>towerse.member.center_of_buoyancy</t>
+          <t>towerse.member.nodes_r</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -7610,7 +7141,7 @@
       </c>
       <c r="D310" t="inlineStr">
         <is>
-          <t>[0. 0. 0.]</t>
+          <t>[3.0, 2.8225, 2.645, 2.4675, 2.29, 2.1125, 1.935]</t>
         </is>
       </c>
       <c r="E310" t="inlineStr"/>
@@ -7618,7 +7149,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>towerse.member.displacement</t>
+          <t>towerse.member.center_of_buoyancy</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -7628,12 +7159,12 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>m**3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E311" t="inlineStr"/>
@@ -7641,7 +7172,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>towerse.member.buoyancy_force</t>
+          <t>towerse.member.displacement</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -7651,20 +7182,18 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>N</t>
-        </is>
-      </c>
-      <c r="D312" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m**3</t>
+        </is>
+      </c>
+      <c r="D312" t="n">
+        <v>0</v>
       </c>
       <c r="E312" t="inlineStr"/>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>towerse.member.idx_cb</t>
+          <t>towerse.member.buoyancy_force</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -7672,18 +7201,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C313" t="inlineStr"/>
-      <c r="D313" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>N</t>
+        </is>
+      </c>
+      <c r="D313" t="n">
+        <v>0</v>
       </c>
       <c r="E313" t="inlineStr"/>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>towerse.member.Awater</t>
+          <t>towerse.member.idx_cb</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -7691,22 +7222,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C314" t="inlineStr">
-        <is>
-          <t>m**2</t>
-        </is>
-      </c>
-      <c r="D314" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C314" t="inlineStr"/>
+      <c r="D314" t="n">
+        <v>0</v>
       </c>
       <c r="E314" t="inlineStr"/>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>towerse.member.Iwaterx</t>
+          <t>towerse.member.Awater</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -7716,20 +7241,18 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>m**4</t>
-        </is>
-      </c>
-      <c r="D315" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m**2</t>
+        </is>
+      </c>
+      <c r="D315" t="n">
+        <v>0</v>
       </c>
       <c r="E315" t="inlineStr"/>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>towerse.member.Iwatery</t>
+          <t>towerse.member.Iwaterx</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -7742,17 +7265,15 @@
           <t>m**4</t>
         </is>
       </c>
-      <c r="D316" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D316" t="n">
+        <v>0</v>
       </c>
       <c r="E316" t="inlineStr"/>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>towerse.member.added_mass</t>
+          <t>towerse.member.Iwatery</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -7762,20 +7283,18 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D317" t="inlineStr">
-        <is>
-          <t>[0. 0. 0. 0. 0. 0.]</t>
-        </is>
+          <t>m**4</t>
+        </is>
+      </c>
+      <c r="D317" t="n">
+        <v>0</v>
       </c>
       <c r="E317" t="inlineStr"/>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>towerse.member.waterline_centroid</t>
+          <t>towerse.member.added_mass</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -7785,12 +7304,12 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0, 0.0, 0.0, 0.0, 0.0]</t>
         </is>
       </c>
       <c r="E318" t="inlineStr"/>
@@ -7798,7 +7317,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>towerse.member.z_dim</t>
+          <t>towerse.member.waterline_centroid</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -7813,7 +7332,7 @@
       </c>
       <c r="D319" t="inlineStr">
         <is>
-          <t>[ 0. 15. 30. 45. 60. 75. 90.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E319" t="inlineStr"/>
@@ -7821,7 +7340,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>towerse.member.d_eff</t>
+          <t>towerse.member.z_dim</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -7836,7 +7355,7 @@
       </c>
       <c r="D320" t="inlineStr">
         <is>
-          <t>[6.    5.645 5.29  4.935 4.58  4.225 3.87 ]</t>
+          <t>[0.0, 15.0, 30.0, 45.0, 60.0, 75.0, 90.0]</t>
         </is>
       </c>
       <c r="E320" t="inlineStr"/>
@@ -7844,7 +7363,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>towerse.tower_section_height</t>
+          <t>towerse.member.d_eff</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -7859,7 +7378,7 @@
       </c>
       <c r="D321" t="inlineStr">
         <is>
-          <t>[45. 45.]</t>
+          <t>[6.0, 5.645, 5.29, 4.935, 4.58, 4.225, 3.87]</t>
         </is>
       </c>
       <c r="E321" t="inlineStr"/>
@@ -7867,7 +7386,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>towerse.member.sigma_ult</t>
+          <t>towerse.tower_section_height</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -7877,12 +7396,12 @@
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
         <is>
-          <t>[1.12e+09 1.12e+09]</t>
+          <t>[45.0, 45.0]</t>
         </is>
       </c>
       <c r="E322" t="inlineStr"/>
@@ -7890,7 +7409,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>towerse.member.wohler_exp</t>
+          <t>towerse.member.sigma_ult</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -7898,10 +7417,14 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C323" t="inlineStr"/>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>[3. 3.]</t>
+          <t>[1120000000.0, 1120000000.0]</t>
         </is>
       </c>
       <c r="E323" t="inlineStr"/>
@@ -7909,7 +7432,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>towerse.member.wohler_A</t>
+          <t>towerse.member.wohler_exp</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -7920,7 +7443,7 @@
       <c r="C324" t="inlineStr"/>
       <c r="D324" t="inlineStr">
         <is>
-          <t>[3.55346484e+10 3.55346484e+10]</t>
+          <t>[3.0, 3.0]</t>
         </is>
       </c>
       <c r="E324" t="inlineStr"/>
@@ -7928,7 +7451,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>towerse.member.ballast_density</t>
+          <t>towerse.member.wohler_A</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -7936,14 +7459,10 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C325" t="inlineStr">
-        <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
+      <c r="C325" t="inlineStr"/>
       <c r="D325" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[35534648443.719765, 35534648443.719765]</t>
         </is>
       </c>
       <c r="E325" t="inlineStr"/>
@@ -7951,7 +7470,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>towerse.member.ballast_unit_cost</t>
+          <t>towerse.member.ballast_density</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -7961,7 +7480,7 @@
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>USD/kg</t>
+          <t>kg/m**3</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -7974,7 +7493,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>towerse.z_param</t>
+          <t>towerse.member.ballast_unit_cost</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -7984,12 +7503,12 @@
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>USD/kg</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>[ 0. 45. 90.]</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="E327" t="inlineStr"/>
@@ -7997,7 +7516,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>towerse.member.sec_loc</t>
+          <t>towerse.z_param</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -8005,22 +7524,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C328" t="inlineStr"/>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D328" t="inlineStr">
         <is>
-          <t>[0. 1.]</t>
-        </is>
-      </c>
-      <c r="E328" t="inlineStr">
-        <is>
-          <t>normalized sectional location</t>
-        </is>
-      </c>
+          <t>[0.0, 45.0, 90.0]</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr"/>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
-          <t>towerse.member.str_tw</t>
+          <t>towerse.member.sec_loc</t>
         </is>
       </c>
       <c r="B329" t="inlineStr">
@@ -8028,26 +7547,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C329" t="inlineStr">
-        <is>
-          <t>deg</t>
-        </is>
-      </c>
+      <c r="C329" t="inlineStr"/>
       <c r="D329" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 1.0]</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>structural twist of section</t>
+          <t>normalized sectional location</t>
         </is>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
         <is>
-          <t>towerse.member.tw_iner</t>
+          <t>towerse.member.str_tw</t>
         </is>
       </c>
       <c r="B330" t="inlineStr">
@@ -8062,19 +7577,19 @@
       </c>
       <c r="D330" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E330" t="inlineStr">
         <is>
-          <t>inertial twist of section</t>
+          <t>structural twist of section</t>
         </is>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
         <is>
-          <t>towerse.member.mass_den</t>
+          <t>towerse.member.tw_iner</t>
         </is>
       </c>
       <c r="B331" t="inlineStr">
@@ -8084,24 +7599,24 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>kg/m</t>
+          <t>deg</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>[3510.69996926 2366.7802451 ]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>sectional mass per unit length</t>
+          <t>inertial twist of section</t>
         </is>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
         <is>
-          <t>towerse.member.foreaft_iner</t>
+          <t>towerse.member.mass_den</t>
         </is>
       </c>
       <c r="B332" t="inlineStr">
@@ -8111,24 +7626,24 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>kg*m</t>
+          <t>kg/m</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
         <is>
-          <t>[13000.89678448  5680.70806693]</t>
+          <t>[3510.6999692581417, 2366.780245100547]</t>
         </is>
       </c>
       <c r="E332" t="inlineStr">
         <is>
-          <t>sectional fore-aft intertia per unit length about the Y_G inertia axis</t>
+          <t>sectional mass per unit length</t>
         </is>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>towerse.member.sideside_iner</t>
+          <t>towerse.member.foreaft_iner</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
@@ -8143,19 +7658,19 @@
       </c>
       <c r="D333" t="inlineStr">
         <is>
-          <t>[13000.89678448  5680.70806693]</t>
+          <t>[13000.896784480998, 5680.708066930962]</t>
         </is>
       </c>
       <c r="E333" t="inlineStr">
         <is>
-          <t>sectional side-side intertia per unit length about the Y_G inertia axis</t>
+          <t>sectional fore-aft intertia per unit length about the Y_G inertia axis</t>
         </is>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>towerse.member.foreaft_stff</t>
+          <t>towerse.member.sideside_iner</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
@@ -8165,24 +7680,24 @@
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>N*m**2</t>
+          <t>kg*m</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
         <is>
-          <t>[3.11547970e+11 1.36130076e+11]</t>
+          <t>[13000.896784480998, 5680.708066930962]</t>
         </is>
       </c>
       <c r="E334" t="inlineStr">
         <is>
-          <t>sectional fore-aft bending stiffness per unit length about the Y_E elastic axis</t>
+          <t>sectional side-side intertia per unit length about the Y_G inertia axis</t>
         </is>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
         <is>
-          <t>towerse.member.sideside_stff</t>
+          <t>towerse.member.foreaft_stff</t>
         </is>
       </c>
       <c r="B335" t="inlineStr">
@@ -8197,19 +7712,19 @@
       </c>
       <c r="D335" t="inlineStr">
         <is>
-          <t>[3.11547970e+11 1.36130076e+11]</t>
+          <t>[311547969913.27576, 136130075890.98878]</t>
         </is>
       </c>
       <c r="E335" t="inlineStr">
         <is>
-          <t>sectional side-side bending stiffness per unit length about the Y_E elastic axis</t>
+          <t>sectional fore-aft bending stiffness per unit length about the Y_E elastic axis</t>
         </is>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
         <is>
-          <t>towerse.member.tor_stff</t>
+          <t>towerse.member.sideside_stff</t>
         </is>
       </c>
       <c r="B336" t="inlineStr">
@@ -8224,19 +7739,19 @@
       </c>
       <c r="D336" t="inlineStr">
         <is>
-          <t>[2.4705754e+11 1.0795115e+11]</t>
+          <t>[311547969913.27576, 136130075890.98878]</t>
         </is>
       </c>
       <c r="E336" t="inlineStr">
         <is>
-          <t>sectional torsional stiffness</t>
+          <t>sectional side-side bending stiffness per unit length about the Y_E elastic axis</t>
         </is>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
         <is>
-          <t>towerse.member.axial_stff</t>
+          <t>towerse.member.tor_stff</t>
         </is>
       </c>
       <c r="B337" t="inlineStr">
@@ -8246,24 +7761,24 @@
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>N</t>
+          <t>N*m**2</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>[8.41289233e+10 5.67165168e+10]</t>
+          <t>[247057540141.22766, 107951150181.55411]</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
         <is>
-          <t>sectional axial stiffness</t>
+          <t>sectional torsional stiffness</t>
         </is>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
         <is>
-          <t>towerse.member.cg_offst</t>
+          <t>towerse.member.axial_stff</t>
         </is>
       </c>
       <c r="B338" t="inlineStr">
@@ -8273,24 +7788,24 @@
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>N</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[84128923298.78125, 56716516776.91222]</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>offset from the sectional center of mass</t>
+          <t>sectional axial stiffness</t>
         </is>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
         <is>
-          <t>towerse.member.sc_offst</t>
+          <t>towerse.member.cg_offst</t>
         </is>
       </c>
       <c r="B339" t="inlineStr">
@@ -8305,19 +7820,19 @@
       </c>
       <c r="D339" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E339" t="inlineStr">
         <is>
-          <t>offset from the sectional shear center</t>
+          <t>offset from the sectional center of mass</t>
         </is>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
         <is>
-          <t>towerse.member.tc_offst</t>
+          <t>towerse.member.sc_offst</t>
         </is>
       </c>
       <c r="B340" t="inlineStr">
@@ -8332,19 +7847,19 @@
       </c>
       <c r="D340" t="inlineStr">
         <is>
-          <t>[0. 0.]</t>
+          <t>[0.0, 0.0]</t>
         </is>
       </c>
       <c r="E340" t="inlineStr">
         <is>
-          <t>offset from the sectional tension center</t>
+          <t>offset from the sectional shear center</t>
         </is>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
         <is>
-          <t>towerse.member.axial_load2stress</t>
+          <t>towerse.member.tc_offst</t>
         </is>
       </c>
       <c r="B341" t="inlineStr">
@@ -8354,21 +7869,24 @@
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>m**2</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
         <is>
-          <t>[[0.         0.         2.37730369 1.75494644 1.75494644 0.        ]
- [0.         0.         3.52630964 3.23403919 3.23403919 0.        ]]</t>
-        </is>
-      </c>
-      <c r="E341" t="inlineStr"/>
+          <t>[0.0, 0.0]</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>offset from the sectional tension center</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
         <is>
-          <t>towerse.member.shear_load2stress</t>
+          <t>towerse.member.axial_load2stress</t>
         </is>
       </c>
       <c r="B342" t="inlineStr">
@@ -8383,8 +7901,7 @@
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>[[3.90738716 3.90738716 0.         0.         0.         0.87747322]
- [5.79544339 5.79544339 0.         0.         0.         1.61701959]]</t>
+          <t>[[0.0, 0.0, 2.377303692449578, 1.7549464377899697, 1.7549464377899697, 0.0], [0.0, 0.0, 3.526309642509899, 3.234039187288388, 3.234039187288388, 0.0]]</t>
         </is>
       </c>
       <c r="E342" t="inlineStr"/>
@@ -8392,7 +7909,7 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>towerse.member.labor_hours</t>
+          <t>towerse.member.shear_load2stress</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
@@ -8402,12 +7919,12 @@
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>h</t>
+          <t>m**2</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
         <is>
-          <t>[217.20991395]</t>
+          <t>[[3.907387159282199, 3.907387159282199, 0.0, 0.0, 0.0, 0.8774732188949849], [5.795443388190964, 5.795443388190964, 0.0, 0.0, 0.0, 1.617019593644194]]</t>
         </is>
       </c>
       <c r="E343" t="inlineStr"/>
@@ -8415,7 +7932,7 @@
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>towerse.tower_cost</t>
+          <t>towerse.member.labor_hours</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
@@ -8425,20 +7942,18 @@
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D344" t="inlineStr">
-        <is>
-          <t>[781256.20935988]</t>
-        </is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="D344" t="n">
+        <v>217.2099139460697</v>
       </c>
       <c r="E344" t="inlineStr"/>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
         <is>
-          <t>towerse.member.section_D</t>
+          <t>towerse.tower_cost</t>
         </is>
       </c>
       <c r="B345" t="inlineStr">
@@ -8448,20 +7963,18 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D345" t="inlineStr">
-        <is>
-          <t>[5.8225 5.4675 5.1125 4.7575 4.4025 4.0475]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D345" t="n">
+        <v>781256.2093598775</v>
       </c>
       <c r="E345" t="inlineStr"/>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
         <is>
-          <t>towerse.member.section_t</t>
+          <t>towerse.member.section_D</t>
         </is>
       </c>
       <c r="B346" t="inlineStr">
@@ -8476,7 +7989,7 @@
       </c>
       <c r="D346" t="inlineStr">
         <is>
-          <t>[0.026322 0.026322 0.026322 0.022042 0.022042 0.022042]</t>
+          <t>[5.8225, 5.467499999999999, 5.1125, 4.7575, 4.4025, 4.047499999999999]</t>
         </is>
       </c>
       <c r="E346" t="inlineStr"/>
@@ -8484,7 +7997,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>towerse.member.section_sigma_y</t>
+          <t>towerse.member.section_t</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -8494,12 +8007,12 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Pa</t>
+          <t>m</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
         <is>
-          <t>[3.45e+08 3.45e+08 3.45e+08 3.45e+08 3.45e+08 3.45e+08]</t>
+          <t>[0.026322, 0.026322, 0.026322, 0.022042000000000003, 0.022042000000000003, 0.022042000000000003]</t>
         </is>
       </c>
       <c r="E347" t="inlineStr"/>
@@ -8507,7 +8020,7 @@
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>towerse.height_constraint</t>
+          <t>towerse.member.section_sigma_y</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -8517,12 +8030,12 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Pa</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>[0.]</t>
+          <t>[345000000.0, 345000000.0, 345000000.0, 345000000.0, 345000000.0, 345000000.0]</t>
         </is>
       </c>
       <c r="E348" t="inlineStr"/>
@@ -8530,7 +8043,7 @@
     <row r="349">
       <c r="A349" t="inlineStr">
         <is>
-          <t>towerse.transition_piece_height</t>
+          <t>towerse.height_constraint</t>
         </is>
       </c>
       <c r="B349" t="inlineStr">
@@ -8543,17 +8056,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D349" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D349" t="n">
+        <v>0</v>
       </c>
       <c r="E349" t="inlineStr"/>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
         <is>
-          <t>towerse.z_start</t>
+          <t>towerse.transition_piece_height</t>
         </is>
       </c>
       <c r="B350" t="inlineStr">
@@ -8566,17 +8077,15 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D350" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D350" t="n">
+        <v>0</v>
       </c>
       <c r="E350" t="inlineStr"/>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
         <is>
-          <t>configuration.rated_power</t>
+          <t>towerse.z_start</t>
         </is>
       </c>
       <c r="B351" t="inlineStr">
@@ -8586,24 +8095,18 @@
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>W</t>
-        </is>
-      </c>
-      <c r="D351" t="inlineStr">
-        <is>
-          <t>[5000000.]</t>
-        </is>
-      </c>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>Electrical rated power of the generator.</t>
-        </is>
-      </c>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D351" t="n">
+        <v>0</v>
+      </c>
+      <c r="E351" t="inlineStr"/>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
         <is>
-          <t>configuration.lifetime</t>
+          <t>configuration.rated_power</t>
         </is>
       </c>
       <c r="B352" t="inlineStr">
@@ -8613,24 +8116,22 @@
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>year</t>
-        </is>
-      </c>
-      <c r="D352" t="inlineStr">
-        <is>
-          <t>[25.]</t>
-        </is>
+          <t>W</t>
+        </is>
+      </c>
+      <c r="D352" t="n">
+        <v>5000000</v>
       </c>
       <c r="E352" t="inlineStr">
         <is>
-          <t>Turbine design lifetime.</t>
+          <t>Electrical rated power of the generator.</t>
         </is>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
         <is>
-          <t>configuration.rotor_diameter_user</t>
+          <t>configuration.lifetime</t>
         </is>
       </c>
       <c r="B353" t="inlineStr">
@@ -8640,24 +8141,22 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D353" t="inlineStr">
-        <is>
-          <t>[126.]</t>
-        </is>
+          <t>year</t>
+        </is>
+      </c>
+      <c r="D353" t="n">
+        <v>25</v>
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>Diameter of the rotor specified by the user. It is defined as two times the blade length plus the hub diameter.</t>
+          <t>Turbine design lifetime.</t>
         </is>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
         <is>
-          <t>configuration.hub_height_user</t>
+          <t>configuration.rotor_diameter_user</t>
         </is>
       </c>
       <c r="B354" t="inlineStr">
@@ -8670,21 +8169,19 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D354" t="inlineStr">
-        <is>
-          <t>[90.]</t>
-        </is>
+      <c r="D354" t="n">
+        <v>126</v>
       </c>
       <c r="E354" t="inlineStr">
         <is>
-          <t>Height of the hub center over the ground (land-based) or the mean sea level (offshore) specified by the user.</t>
+          <t>Diameter of the rotor specified by the user. It is defined as two times the blade length plus the hub diameter.</t>
         </is>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>configuration.ws_class</t>
+          <t>configuration.hub_height_user</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
@@ -8694,24 +8191,22 @@
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D355" t="inlineStr">
-        <is>
-          <t>I</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D355" t="n">
+        <v>90</v>
       </c>
       <c r="E355" t="inlineStr">
         <is>
-          <t>IEC wind turbine class. I - offshore, II coastal, III - land-based, IV - low wind speed site.</t>
+          <t>Height of the hub center over the ground (land-based) or the mean sea level (offshore) specified by the user.</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>configuration.turb_class</t>
+          <t>configuration.ws_class</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
@@ -8726,19 +8221,19 @@
       </c>
       <c r="D356" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>I</t>
         </is>
       </c>
       <c r="E356" t="inlineStr">
         <is>
-          <t>IEC wind turbine category. A - high turbulence intensity (land-based), B - mid turbulence, C - low turbulence (offshore).</t>
+          <t>IEC wind turbine class. I - offshore, II coastal, III - land-based, IV - low wind speed site.</t>
         </is>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
         <is>
-          <t>configuration.gearbox_type</t>
+          <t>configuration.turb_class</t>
         </is>
       </c>
       <c r="B357" t="inlineStr">
@@ -8753,19 +8248,19 @@
       </c>
       <c r="D357" t="inlineStr">
         <is>
-          <t>geared</t>
+          <t>B</t>
         </is>
       </c>
       <c r="E357" t="inlineStr">
         <is>
-          <t>Gearbox configuration (geared, direct-drive, etc.).</t>
+          <t>IEC wind turbine category. A - high turbulence intensity (land-based), B - mid turbulence, C - low turbulence (offshore).</t>
         </is>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
         <is>
-          <t>configuration.rotor_orientation</t>
+          <t>configuration.gearbox_type</t>
         </is>
       </c>
       <c r="B358" t="inlineStr">
@@ -8780,19 +8275,19 @@
       </c>
       <c r="D358" t="inlineStr">
         <is>
-          <t>upwind</t>
+          <t>geared</t>
         </is>
       </c>
       <c r="E358" t="inlineStr">
         <is>
-          <t>Rotor orientation, either upwind or downwind.</t>
+          <t>Gearbox configuration (geared, direct-drive, etc.).</t>
         </is>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
         <is>
-          <t>configuration.upwind</t>
+          <t>configuration.rotor_orientation</t>
         </is>
       </c>
       <c r="B359" t="inlineStr">
@@ -8805,19 +8300,21 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="D359" t="b">
-        <v>1</v>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>upwind</t>
+        </is>
       </c>
       <c r="E359" t="inlineStr">
         <is>
-          <t>Convenient boolean for upwind (True) or downwind (False).</t>
+          <t>Rotor orientation, either upwind or downwind.</t>
         </is>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
         <is>
-          <t>configuration.n_blades</t>
+          <t>configuration.upwind</t>
         </is>
       </c>
       <c r="B360" t="inlineStr">
@@ -8830,19 +8327,19 @@
           <t>n/a</t>
         </is>
       </c>
-      <c r="D360" t="n">
-        <v>3</v>
+      <c r="D360" t="b">
+        <v>1</v>
       </c>
       <c r="E360" t="inlineStr">
         <is>
-          <t>Number of blades of the rotor.</t>
+          <t>Convenient boolean for upwind (True) or downwind (False).</t>
         </is>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
         <is>
-          <t>costs.offset_tcc_per_kW</t>
+          <t>configuration.n_blades</t>
         </is>
       </c>
       <c r="B361" t="inlineStr">
@@ -8852,24 +8349,22 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>USD/kW</t>
-        </is>
-      </c>
-      <c r="D361" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D361" t="n">
+        <v>3</v>
       </c>
       <c r="E361" t="inlineStr">
         <is>
-          <t>Offset to turbine capital cost</t>
+          <t>Number of blades of the rotor.</t>
         </is>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
         <is>
-          <t>costs.bos_per_kW</t>
+          <t>costs.offset_tcc_per_kW</t>
         </is>
       </c>
       <c r="B362" t="inlineStr">
@@ -8882,21 +8377,19 @@
           <t>USD/kW</t>
         </is>
       </c>
-      <c r="D362" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D362" t="n">
+        <v>0</v>
       </c>
       <c r="E362" t="inlineStr">
         <is>
-          <t>Balance of station/plant capital cost</t>
+          <t>Offset to turbine capital cost</t>
         </is>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
         <is>
-          <t>costs.opex_per_kW</t>
+          <t>costs.bos_per_kW</t>
         </is>
       </c>
       <c r="B363" t="inlineStr">
@@ -8906,24 +8399,22 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>USD/kW/year</t>
-        </is>
-      </c>
-      <c r="D363" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="D363" t="n">
+        <v>0</v>
       </c>
       <c r="E363" t="inlineStr">
         <is>
-          <t>Average annual operational expenditures of the turbine</t>
+          <t>Balance of station/plant capital cost</t>
         </is>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>costs.wake_loss_factor</t>
+          <t>costs.opex_per_kW</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
@@ -8931,22 +8422,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C364" t="inlineStr"/>
-      <c r="D364" t="inlineStr">
-        <is>
-          <t>[0.15]</t>
-        </is>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>USD/kW/year</t>
+        </is>
+      </c>
+      <c r="D364" t="n">
+        <v>0</v>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>The losses in AEP due to waked conditions</t>
+          <t>Average annual operational expenditures of the turbine</t>
         </is>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>costs.fixed_charge_rate</t>
+          <t>costs.wake_loss_factor</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
@@ -8955,21 +8448,19 @@
         </is>
       </c>
       <c r="C365" t="inlineStr"/>
-      <c r="D365" t="inlineStr">
-        <is>
-          <t>[0.075]</t>
-        </is>
+      <c r="D365" t="n">
+        <v>0.15</v>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Fixed charge rate for coe calculation</t>
+          <t>The losses in AEP due to waked conditions</t>
         </is>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
         <is>
-          <t>costs.labor_rate</t>
+          <t>costs.fixed_charge_rate</t>
         </is>
       </c>
       <c r="B366" t="inlineStr">
@@ -8977,22 +8468,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C366" t="inlineStr">
-        <is>
-          <t>USD/h</t>
-        </is>
-      </c>
-      <c r="D366" t="inlineStr">
-        <is>
-          <t>[58.8]</t>
-        </is>
-      </c>
-      <c r="E366" t="inlineStr"/>
+      <c r="C366" t="inlineStr"/>
+      <c r="D366" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>Fixed charge rate for coe calculation</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
         <is>
-          <t>costs.painting_rate</t>
+          <t>costs.labor_rate</t>
         </is>
       </c>
       <c r="B367" t="inlineStr">
@@ -9002,20 +8491,18 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>USD/m**2</t>
-        </is>
-      </c>
-      <c r="D367" t="inlineStr">
-        <is>
-          <t>[30.]</t>
-        </is>
+          <t>USD/h</t>
+        </is>
+      </c>
+      <c r="D367" t="n">
+        <v>58.8</v>
       </c>
       <c r="E367" t="inlineStr"/>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
         <is>
-          <t>costs.blade_mass_cost_coeff</t>
+          <t>costs.painting_rate</t>
         </is>
       </c>
       <c r="B368" t="inlineStr">
@@ -9025,20 +8512,18 @@
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D368" t="inlineStr">
-        <is>
-          <t>[14.6]</t>
-        </is>
+          <t>USD/m**2</t>
+        </is>
+      </c>
+      <c r="D368" t="n">
+        <v>30</v>
       </c>
       <c r="E368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
         <is>
-          <t>costs.hub_mass_cost_coeff</t>
+          <t>costs.blade_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B369" t="inlineStr">
@@ -9051,17 +8536,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D369" t="inlineStr">
-        <is>
-          <t>[3.9]</t>
-        </is>
+      <c r="D369" t="n">
+        <v>14.6</v>
       </c>
       <c r="E369" t="inlineStr"/>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
         <is>
-          <t>costs.pitch_system_mass_cost_coeff</t>
+          <t>costs.hub_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B370" t="inlineStr">
@@ -9074,17 +8557,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D370" t="inlineStr">
-        <is>
-          <t>[22.1]</t>
-        </is>
+      <c r="D370" t="n">
+        <v>3.9</v>
       </c>
       <c r="E370" t="inlineStr"/>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
         <is>
-          <t>costs.spinner_mass_cost_coeff</t>
+          <t>costs.pitch_system_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B371" t="inlineStr">
@@ -9097,17 +8578,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D371" t="inlineStr">
-        <is>
-          <t>[11.1]</t>
-        </is>
+      <c r="D371" t="n">
+        <v>22.1</v>
       </c>
       <c r="E371" t="inlineStr"/>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
         <is>
-          <t>costs.lss_mass_cost_coeff</t>
+          <t>costs.spinner_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B372" t="inlineStr">
@@ -9120,17 +8599,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D372" t="inlineStr">
-        <is>
-          <t>[11.9]</t>
-        </is>
+      <c r="D372" t="n">
+        <v>11.1</v>
       </c>
       <c r="E372" t="inlineStr"/>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
         <is>
-          <t>costs.bearing_mass_cost_coeff</t>
+          <t>costs.lss_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B373" t="inlineStr">
@@ -9143,17 +8620,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D373" t="inlineStr">
-        <is>
-          <t>[4.5]</t>
-        </is>
+      <c r="D373" t="n">
+        <v>11.9</v>
       </c>
       <c r="E373" t="inlineStr"/>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
         <is>
-          <t>costs.gearbox_torque_cost</t>
+          <t>costs.bearing_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B374" t="inlineStr">
@@ -9163,20 +8638,18 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>USD/kN/m</t>
-        </is>
-      </c>
-      <c r="D374" t="inlineStr">
-        <is>
-          <t>[50.]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D374" t="n">
+        <v>4.5</v>
       </c>
       <c r="E374" t="inlineStr"/>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
         <is>
-          <t>costs.hss_mass_cost_coeff</t>
+          <t>costs.gearbox_torque_cost</t>
         </is>
       </c>
       <c r="B375" t="inlineStr">
@@ -9186,20 +8659,18 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D375" t="inlineStr">
-        <is>
-          <t>[6.8]</t>
-        </is>
+          <t>USD/kN/m</t>
+        </is>
+      </c>
+      <c r="D375" t="n">
+        <v>50</v>
       </c>
       <c r="E375" t="inlineStr"/>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
         <is>
-          <t>costs.generator_mass_cost_coeff</t>
+          <t>costs.hss_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B376" t="inlineStr">
@@ -9212,17 +8683,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D376" t="inlineStr">
-        <is>
-          <t>[12.4]</t>
-        </is>
+      <c r="D376" t="n">
+        <v>6.8</v>
       </c>
       <c r="E376" t="inlineStr"/>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
         <is>
-          <t>costs.bedplate_mass_cost_coeff</t>
+          <t>costs.generator_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B377" t="inlineStr">
@@ -9235,17 +8704,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D377" t="inlineStr">
-        <is>
-          <t>[2.9]</t>
-        </is>
+      <c r="D377" t="n">
+        <v>12.4</v>
       </c>
       <c r="E377" t="inlineStr"/>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>costs.yaw_mass_cost_coeff</t>
+          <t>costs.bedplate_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
@@ -9258,17 +8725,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D378" t="inlineStr">
-        <is>
-          <t>[8.3]</t>
-        </is>
+      <c r="D378" t="n">
+        <v>2.9</v>
       </c>
       <c r="E378" t="inlineStr"/>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>costs.converter_mass_cost_coeff</t>
+          <t>costs.yaw_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
@@ -9281,17 +8746,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D379" t="inlineStr">
-        <is>
-          <t>[18.8]</t>
-        </is>
+      <c r="D379" t="n">
+        <v>8.300000000000001</v>
       </c>
       <c r="E379" t="inlineStr"/>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
         <is>
-          <t>costs.transformer_mass_cost_coeff</t>
+          <t>costs.converter_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B380" t="inlineStr">
@@ -9304,17 +8767,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D380" t="inlineStr">
-        <is>
-          <t>[18.8]</t>
-        </is>
+      <c r="D380" t="n">
+        <v>18.8</v>
       </c>
       <c r="E380" t="inlineStr"/>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
         <is>
-          <t>costs.hvac_mass_cost_coeff</t>
+          <t>costs.transformer_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B381" t="inlineStr">
@@ -9327,17 +8788,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D381" t="inlineStr">
-        <is>
-          <t>[124.]</t>
-        </is>
+      <c r="D381" t="n">
+        <v>18.8</v>
       </c>
       <c r="E381" t="inlineStr"/>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
         <is>
-          <t>costs.cover_mass_cost_coeff</t>
+          <t>costs.hvac_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B382" t="inlineStr">
@@ -9350,17 +8809,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D382" t="inlineStr">
-        <is>
-          <t>[5.7]</t>
-        </is>
+      <c r="D382" t="n">
+        <v>124</v>
       </c>
       <c r="E382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
         <is>
-          <t>costs.elec_connec_machine_rating_cost_coeff</t>
+          <t>costs.cover_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B383" t="inlineStr">
@@ -9370,20 +8827,18 @@
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>USD/kW</t>
-        </is>
-      </c>
-      <c r="D383" t="inlineStr">
-        <is>
-          <t>[41.85]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D383" t="n">
+        <v>5.7</v>
       </c>
       <c r="E383" t="inlineStr"/>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
         <is>
-          <t>costs.platforms_mass_cost_coeff</t>
+          <t>costs.elec_connec_machine_rating_cost_coeff</t>
         </is>
       </c>
       <c r="B384" t="inlineStr">
@@ -9393,20 +8848,18 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D384" t="inlineStr">
-        <is>
-          <t>[17.1]</t>
-        </is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="D384" t="n">
+        <v>41.85</v>
       </c>
       <c r="E384" t="inlineStr"/>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
         <is>
-          <t>costs.tower_mass_cost_coeff</t>
+          <t>costs.platforms_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B385" t="inlineStr">
@@ -9419,17 +8872,15 @@
           <t>USD/kg</t>
         </is>
       </c>
-      <c r="D385" t="inlineStr">
-        <is>
-          <t>[2.9]</t>
-        </is>
+      <c r="D385" t="n">
+        <v>17.1</v>
       </c>
       <c r="E385" t="inlineStr"/>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
         <is>
-          <t>costs.controls_machine_rating_cost_coeff</t>
+          <t>costs.tower_mass_cost_coeff</t>
         </is>
       </c>
       <c r="B386" t="inlineStr">
@@ -9439,20 +8890,18 @@
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>USD/kW</t>
-        </is>
-      </c>
-      <c r="D386" t="inlineStr">
-        <is>
-          <t>[21.15]</t>
-        </is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D386" t="n">
+        <v>2.9</v>
       </c>
       <c r="E386" t="inlineStr"/>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
         <is>
-          <t>costs.crane_cost</t>
+          <t>costs.controls_machine_rating_cost_coeff</t>
         </is>
       </c>
       <c r="B387" t="inlineStr">
@@ -9462,20 +8911,18 @@
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="D387" t="inlineStr">
-        <is>
-          <t>[12000.]</t>
-        </is>
+          <t>USD/kW</t>
+        </is>
+      </c>
+      <c r="D387" t="n">
+        <v>21.15</v>
       </c>
       <c r="E387" t="inlineStr"/>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
         <is>
-          <t>costs.electricity_price</t>
+          <t>costs.crane_cost</t>
         </is>
       </c>
       <c r="B388" t="inlineStr">
@@ -9485,20 +8932,18 @@
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>USD/kW/h</t>
-        </is>
-      </c>
-      <c r="D388" t="inlineStr">
-        <is>
-          <t>[0.04]</t>
-        </is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="D388" t="n">
+        <v>12000</v>
       </c>
       <c r="E388" t="inlineStr"/>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
         <is>
-          <t>costs.reserve_margin_price</t>
+          <t>costs.electricity_price</t>
         </is>
       </c>
       <c r="B389" t="inlineStr">
@@ -9508,20 +8953,18 @@
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>USD/kW/year</t>
-        </is>
-      </c>
-      <c r="D389" t="inlineStr">
-        <is>
-          <t>[120.]</t>
-        </is>
+          <t>USD/kW/h</t>
+        </is>
+      </c>
+      <c r="D389" t="n">
+        <v>0.04</v>
       </c>
       <c r="E389" t="inlineStr"/>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
         <is>
-          <t>costs.capacity_credit</t>
+          <t>costs.reserve_margin_price</t>
         </is>
       </c>
       <c r="B390" t="inlineStr">
@@ -9529,18 +8972,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C390" t="inlineStr"/>
-      <c r="D390" t="inlineStr">
-        <is>
-          <t>[1.]</t>
-        </is>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>USD/kW/year</t>
+        </is>
+      </c>
+      <c r="D390" t="n">
+        <v>120</v>
       </c>
       <c r="E390" t="inlineStr"/>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
         <is>
-          <t>costs.benchmark_price</t>
+          <t>costs.capacity_credit</t>
         </is>
       </c>
       <c r="B391" t="inlineStr">
@@ -9548,22 +8993,16 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C391" t="inlineStr">
-        <is>
-          <t>USD/kW/h</t>
-        </is>
-      </c>
-      <c r="D391" t="inlineStr">
-        <is>
-          <t>[0.071]</t>
-        </is>
+      <c r="C391" t="inlineStr"/>
+      <c r="D391" t="n">
+        <v>1</v>
       </c>
       <c r="E391" t="inlineStr"/>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
         <is>
-          <t>costs.turbine_number</t>
+          <t>costs.benchmark_price</t>
         </is>
       </c>
       <c r="B392" t="inlineStr">
@@ -9573,22 +9012,18 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>USD/kW/h</t>
         </is>
       </c>
       <c r="D392" t="n">
-        <v>50</v>
-      </c>
-      <c r="E392" t="inlineStr">
-        <is>
-          <t>Number of turbines at plant</t>
-        </is>
-      </c>
+        <v>0.07099999999999999</v>
+      </c>
+      <c r="E392" t="inlineStr"/>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
         <is>
-          <t>env.rho_air</t>
+          <t>costs.turbine_number</t>
         </is>
       </c>
       <c r="B393" t="inlineStr">
@@ -9598,24 +9033,22 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D393" t="inlineStr">
-        <is>
-          <t>[1.225]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D393" t="n">
+        <v>50</v>
       </c>
       <c r="E393" t="inlineStr">
         <is>
-          <t>Density of air</t>
+          <t>Number of turbines at plant</t>
         </is>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>env.mu_air</t>
+          <t>env.rho_air</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
@@ -9625,24 +9058,22 @@
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>kg/m/s</t>
-        </is>
-      </c>
-      <c r="D394" t="inlineStr">
-        <is>
-          <t>[1.81e-05]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D394" t="n">
+        <v>1.225</v>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Dynamic viscosity of air</t>
+          <t>Density of air</t>
         </is>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>env.shear_exp</t>
+          <t>env.mu_air</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
@@ -9650,22 +9081,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C395" t="inlineStr"/>
-      <c r="D395" t="inlineStr">
-        <is>
-          <t>[0.2]</t>
-        </is>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>kg/m/s</t>
+        </is>
+      </c>
+      <c r="D395" t="n">
+        <v>1.81e-05</v>
       </c>
       <c r="E395" t="inlineStr">
         <is>
-          <t>Shear exponent of the wind.</t>
+          <t>Dynamic viscosity of air</t>
         </is>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>env.speed_sound_air</t>
+          <t>env.shear_exp</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
@@ -9673,26 +9106,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C396" t="inlineStr">
-        <is>
-          <t>m/s</t>
-        </is>
-      </c>
-      <c r="D396" t="inlineStr">
-        <is>
-          <t>[340.]</t>
-        </is>
+      <c r="C396" t="inlineStr"/>
+      <c r="D396" t="n">
+        <v>0.2</v>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Speed of sound in air.</t>
+          <t>Shear exponent of the wind.</t>
         </is>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
         <is>
-          <t>env.weibull_k</t>
+          <t>env.speed_sound_air</t>
         </is>
       </c>
       <c r="B397" t="inlineStr">
@@ -9700,22 +9127,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C397" t="inlineStr"/>
-      <c r="D397" t="inlineStr">
-        <is>
-          <t>[2.]</t>
-        </is>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>m/s</t>
+        </is>
+      </c>
+      <c r="D397" t="n">
+        <v>340</v>
       </c>
       <c r="E397" t="inlineStr">
         <is>
-          <t>Shape parameter of the Weibull probability density function of the wind.</t>
+          <t>Speed of sound in air.</t>
         </is>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
         <is>
-          <t>env.rho_water</t>
+          <t>env.weibull_k</t>
         </is>
       </c>
       <c r="B398" t="inlineStr">
@@ -9723,26 +9152,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C398" t="inlineStr">
-        <is>
-          <t>kg/m**3</t>
-        </is>
-      </c>
-      <c r="D398" t="inlineStr">
-        <is>
-          <t>[1025.]</t>
-        </is>
+      <c r="C398" t="inlineStr"/>
+      <c r="D398" t="n">
+        <v>2</v>
       </c>
       <c r="E398" t="inlineStr">
         <is>
-          <t>Density of ocean water</t>
+          <t>Shape parameter of the Weibull probability density function of the wind.</t>
         </is>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>env.mu_water</t>
+          <t>env.rho_water</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -9752,24 +9175,22 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>kg/m/s</t>
-        </is>
-      </c>
-      <c r="D399" t="inlineStr">
-        <is>
-          <t>[0.0013351]</t>
-        </is>
+          <t>kg/m**3</t>
+        </is>
+      </c>
+      <c r="D399" t="n">
+        <v>1025</v>
       </c>
       <c r="E399" t="inlineStr">
         <is>
-          <t>Dynamic viscosity of ocean water</t>
+          <t>Density of ocean water</t>
         </is>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>env.water_depth</t>
+          <t>env.mu_water</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -9779,24 +9200,22 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D400" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg/m/s</t>
+        </is>
+      </c>
+      <c r="D400" t="n">
+        <v>0.0013351</v>
       </c>
       <c r="E400" t="inlineStr">
         <is>
-          <t>Water depth for analysis.  Values &gt; 0 mean offshore</t>
+          <t>Dynamic viscosity of ocean water</t>
         </is>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>env.Hsig_wave</t>
+          <t>env.water_depth</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
@@ -9809,21 +9228,19 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D401" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D401" t="n">
+        <v>0</v>
       </c>
       <c r="E401" t="inlineStr">
         <is>
-          <t>Significant wave height</t>
+          <t>Water depth for analysis.  Values &gt; 0 mean offshore</t>
         </is>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>env.Tsig_wave</t>
+          <t>env.Hsig_wave</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
@@ -9833,24 +9250,22 @@
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>s</t>
-        </is>
-      </c>
-      <c r="D402" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D402" t="n">
+        <v>0</v>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Significant wave period</t>
+          <t>Significant wave height</t>
         </is>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>env.G_soil</t>
+          <t>env.Tsig_wave</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
@@ -9860,24 +9275,22 @@
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>N/m**2</t>
-        </is>
-      </c>
-      <c r="D403" t="inlineStr">
-        <is>
-          <t>[1.4e+08]</t>
-        </is>
+          <t>s</t>
+        </is>
+      </c>
+      <c r="D403" t="n">
+        <v>0</v>
       </c>
       <c r="E403" t="inlineStr">
         <is>
-          <t>Shear stress of soil</t>
+          <t>Significant wave period</t>
         </is>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>env.nu_soil</t>
+          <t>env.G_soil</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
@@ -9885,22 +9298,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C404" t="inlineStr"/>
-      <c r="D404" t="inlineStr">
-        <is>
-          <t>[0.4]</t>
-        </is>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>N/m**2</t>
+        </is>
+      </c>
+      <c r="D404" t="n">
+        <v>140000000</v>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Poisson ratio of soil</t>
+          <t>Shear stress of soil</t>
         </is>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
         <is>
-          <t>high_level_tower_props.tower_ref_axis</t>
+          <t>env.nu_soil</t>
         </is>
       </c>
       <c r="B405" t="inlineStr">
@@ -9908,28 +9323,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C405" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D405" t="inlineStr">
-        <is>
-          <t>[[ 0.  0.  0.]
- [ 0.  0. 45.]
- [ 0.  0. 90.]]</t>
-        </is>
+      <c r="C405" t="inlineStr"/>
+      <c r="D405" t="n">
+        <v>0.4</v>
       </c>
       <c r="E405" t="inlineStr">
         <is>
-          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
+          <t>Poisson ratio of soil</t>
         </is>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
         <is>
-          <t>high_level_tower_props.hub_height</t>
+          <t>high_level_tower_props.tower_ref_axis</t>
         </is>
       </c>
       <c r="B406" t="inlineStr">
@@ -9944,19 +9351,19 @@
       </c>
       <c r="D406" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 45.0], [0.0, 0.0, 90.0]]</t>
         </is>
       </c>
       <c r="E406" t="inlineStr">
         <is>
-          <t>Height of the hub in the global reference system, i.e. distance rotor center to ground.</t>
+          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
         </is>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
         <is>
-          <t>materials.ply_t</t>
+          <t>high_level_tower_props.hub_height</t>
         </is>
       </c>
       <c r="B407" t="inlineStr">
@@ -9969,21 +9376,19 @@
           <t>m</t>
         </is>
       </c>
-      <c r="D407" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D407" t="n">
+        <v>90</v>
       </c>
       <c r="E407" t="inlineStr">
         <is>
-          <t>1D array of the ply thicknesses of the materials. Non-composite materials are kept at 0.</t>
+          <t>Height of the hub in the global reference system, i.e. distance rotor center to ground.</t>
         </is>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
         <is>
-          <t>materials.fvf</t>
+          <t>materials.ply_t</t>
         </is>
       </c>
       <c r="B408" t="inlineStr">
@@ -9991,22 +9396,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C408" t="inlineStr"/>
-      <c r="D408" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D408" t="n">
+        <v>0</v>
       </c>
       <c r="E408" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional fiber volume fraction of the composite materials. Non-composite materials are kept at 0.</t>
+          <t>1D array of the ply thicknesses of the materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>materials.fwf</t>
+          <t>materials.fvf</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -10015,21 +9422,19 @@
         </is>
       </c>
       <c r="C409" t="inlineStr"/>
-      <c r="D409" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="D409" t="n">
+        <v>0</v>
       </c>
       <c r="E409" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional fiber weight- fraction of the composite materials. Non-composite materials are kept at 0.</t>
+          <t>1D array of the non-dimensional fiber volume fraction of the composite materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>materials.E</t>
+          <t>materials.fwf</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -10037,26 +9442,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C410" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
-      <c r="D410" t="inlineStr">
-        <is>
-          <t>[[2.e+11 2.e+11 2.e+11]]</t>
-        </is>
+      <c r="C410" t="inlineStr"/>
+      <c r="D410" t="n">
+        <v>0</v>
       </c>
       <c r="E410" t="inlineStr">
         <is>
-          <t>2D array of the Youngs moduli of the materials. Each row represents a material, the three columns represent E11, E22 and E33.</t>
+          <t>1D array of the non-dimensional fiber weight- fraction of the composite materials. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
         <is>
-          <t>materials.G</t>
+          <t>materials.E</t>
         </is>
       </c>
       <c r="B411" t="inlineStr">
@@ -10071,19 +9470,19 @@
       </c>
       <c r="D411" t="inlineStr">
         <is>
-          <t>[[7.93e+10 7.93e+10 7.93e+10]]</t>
+          <t>[[200000000000.0, 200000000000.0, 200000000000.0]]</t>
         </is>
       </c>
       <c r="E411" t="inlineStr">
         <is>
-          <t>2D array of the shear moduli of the materials. Each row represents a material, the three columns represent G12, G13 and G23.</t>
+          <t>2D array of the Youngs moduli of the materials. Each row represents a material, the three columns represent E11, E22 and E33.</t>
         </is>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
         <is>
-          <t>materials.nu</t>
+          <t>materials.G</t>
         </is>
       </c>
       <c r="B412" t="inlineStr">
@@ -10091,22 +9490,26 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
       <c r="D412" t="inlineStr">
         <is>
-          <t>[[0.265 0.265 0.265]]</t>
+          <t>[[79300000000.0, 79300000000.0, 79300000000.0]]</t>
         </is>
       </c>
       <c r="E412" t="inlineStr">
         <is>
-          <t>2D array of the Poisson ratio of the materials. Each row represents a material, the three columns represent nu12, nu13 and nu23.</t>
+          <t>2D array of the shear moduli of the materials. Each row represents a material, the three columns represent G12, G13 and G23.</t>
         </is>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
         <is>
-          <t>materials.Xt</t>
+          <t>materials.nu</t>
         </is>
       </c>
       <c r="B413" t="inlineStr">
@@ -10114,26 +9517,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C413" t="inlineStr">
-        <is>
-          <t>Pa</t>
-        </is>
-      </c>
+      <c r="C413" t="inlineStr"/>
       <c r="D413" t="inlineStr">
         <is>
-          <t>[[1.12e+09 1.12e+09 1.12e+09]]</t>
+          <t>[[0.265, 0.265, 0.265]]</t>
         </is>
       </c>
       <c r="E413" t="inlineStr">
         <is>
-          <t>2D array of the Ultimate Tensile Strength (UTS) of the materials. Each row represents a material, the three columns represent Xt12, Xt13 and Xt23.</t>
+          <t>2D array of the Poisson ratio of the materials. Each row represents a material, the three columns represent nu12, nu13 and nu23.</t>
         </is>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
         <is>
-          <t>materials.Xc</t>
+          <t>materials.Xt</t>
         </is>
       </c>
       <c r="B414" t="inlineStr">
@@ -10148,19 +9547,19 @@
       </c>
       <c r="D414" t="inlineStr">
         <is>
-          <t>[[2.16e+09 2.16e+09 2.16e+09]]</t>
+          <t>[[1120000000.0, 1120000000.0, 1120000000.0]]</t>
         </is>
       </c>
       <c r="E414" t="inlineStr">
         <is>
-          <t>2D array of the Ultimate Compressive Strength (UCS) of the materials. Each row represents a material, the three columns represent Xc12, Xc13 and Xc23.</t>
+          <t>2D array of the Ultimate Tensile Strength (UTS) of the materials. Each row represents a material, the three columns represent Xt12, Xt13 and Xt23.</t>
         </is>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>materials.S</t>
+          <t>materials.Xc</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
@@ -10175,19 +9574,19 @@
       </c>
       <c r="D415" t="inlineStr">
         <is>
-          <t>[[0. 0. 0.]]</t>
+          <t>[[2160000000.0, 2160000000.0, 2160000000.0]]</t>
         </is>
       </c>
       <c r="E415" t="inlineStr">
         <is>
-          <t>2D array of the Ultimate Shear Strength (USS) of the materials. Each row represents a material, the three columns represent S12, S13 and S23.</t>
+          <t>2D array of the Ultimate Compressive Strength (UCS) of the materials. Each row represents a material, the three columns represent Xc12, Xc13 and Xc23.</t>
         </is>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>materials.sigma_y</t>
+          <t>materials.S</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
@@ -10202,19 +9601,19 @@
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>[3.45e+08]</t>
+          <t>[[0.0, 0.0, 0.0]]</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Yield stress of the material (in the principle direction for composites).</t>
+          <t>2D array of the Ultimate Shear Strength (USS) of the materials. Each row represents a material, the three columns represent S12, S13 and S23.</t>
         </is>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
         <is>
-          <t>materials.wohler_exp</t>
+          <t>materials.sigma_y</t>
         </is>
       </c>
       <c r="B417" t="inlineStr">
@@ -10222,22 +9621,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C417" t="inlineStr"/>
-      <c r="D417" t="inlineStr">
-        <is>
-          <t>[3.]</t>
-        </is>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>Pa</t>
+        </is>
+      </c>
+      <c r="D417" t="n">
+        <v>345000000</v>
       </c>
       <c r="E417" t="inlineStr">
         <is>
-          <t>Exponent of S-N Wohler fatigue curve in the form of S = A*N^-(1/m).</t>
+          <t>Yield stress of the material (in the principle direction for composites).</t>
         </is>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
         <is>
-          <t>materials.wohler_intercept</t>
+          <t>materials.wohler_exp</t>
         </is>
       </c>
       <c r="B418" t="inlineStr">
@@ -10246,21 +9647,19 @@
         </is>
       </c>
       <c r="C418" t="inlineStr"/>
-      <c r="D418" t="inlineStr">
-        <is>
-          <t>[3.55346484e+10]</t>
-        </is>
+      <c r="D418" t="n">
+        <v>3</v>
       </c>
       <c r="E418" t="inlineStr">
         <is>
-          <t>Stress-intercept (A) of S-N Wohler fatigue curve in the form of S = A*N^-(1/m), taken as ultimate stress unless otherwise specified.</t>
+          <t>Exponent of S-N Wohler fatigue curve in the form of S = A*N^-(1/m).</t>
         </is>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
         <is>
-          <t>materials.unit_cost</t>
+          <t>materials.wohler_intercept</t>
         </is>
       </c>
       <c r="B419" t="inlineStr">
@@ -10268,26 +9667,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C419" t="inlineStr">
-        <is>
-          <t>USD/kg</t>
-        </is>
-      </c>
-      <c r="D419" t="inlineStr">
-        <is>
-          <t>[0.7]</t>
-        </is>
+      <c r="C419" t="inlineStr"/>
+      <c r="D419" t="n">
+        <v>35534648443.71976</v>
       </c>
       <c r="E419" t="inlineStr">
         <is>
-          <t>1D array of the unit costs of the materials.</t>
+          <t>Stress-intercept (A) of S-N Wohler fatigue curve in the form of S = A*N^-(1/m), taken as ultimate stress unless otherwise specified.</t>
         </is>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
         <is>
-          <t>materials.waste</t>
+          <t>materials.unit_cost</t>
         </is>
       </c>
       <c r="B420" t="inlineStr">
@@ -10295,22 +9688,24 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C420" t="inlineStr"/>
-      <c r="D420" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>USD/kg</t>
+        </is>
+      </c>
+      <c r="D420" t="n">
+        <v>0.7</v>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional waste fraction of the materials.</t>
+          <t>1D array of the unit costs of the materials.</t>
         </is>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
         <is>
-          <t>materials.roll_mass</t>
+          <t>materials.waste</t>
         </is>
       </c>
       <c r="B421" t="inlineStr">
@@ -10318,26 +9713,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C421" t="inlineStr">
-        <is>
-          <t>kg</t>
-        </is>
-      </c>
-      <c r="D421" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+      <c r="C421" t="inlineStr"/>
+      <c r="D421" t="n">
+        <v>0</v>
       </c>
       <c r="E421" t="inlineStr">
         <is>
-          <t>1D array of the roll mass of the composite fabrics. Non-composite materials are kept at 0.</t>
+          <t>1D array of the non-dimensional waste fraction of the materials.</t>
         </is>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
         <is>
-          <t>materials.orth</t>
+          <t>materials.roll_mass</t>
         </is>
       </c>
       <c r="B422" t="inlineStr">
@@ -10347,24 +9736,22 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D422" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D422" t="n">
+        <v>0</v>
       </c>
       <c r="E422" t="inlineStr">
         <is>
-          <t>1D array of flags to set whether a material is isotropic (0) or orthtropic (1). Each entry represents a material.</t>
+          <t>1D array of the roll mass of the composite fabrics. Non-composite materials are kept at 0.</t>
         </is>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
         <is>
-          <t>tower.ref_axis</t>
+          <t>materials.orth</t>
         </is>
       </c>
       <c r="B423" t="inlineStr">
@@ -10374,26 +9761,22 @@
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>m</t>
-        </is>
-      </c>
-      <c r="D423" t="inlineStr">
-        <is>
-          <t>[[ 0.   0.   0. ]
- [ 0.   0.  43.8]
- [ 0.   0.  87.6]]</t>
-        </is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="D423" t="n">
+        <v>0</v>
       </c>
       <c r="E423" t="inlineStr">
         <is>
-          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
+          <t>1D array of flags to set whether a material is isotropic (0) or orthtropic (1). Each entry represents a material.</t>
         </is>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
         <is>
-          <t>tower.diameter</t>
+          <t>tower.ref_axis</t>
         </is>
       </c>
       <c r="B424" t="inlineStr">
@@ -10408,19 +9791,19 @@
       </c>
       <c r="D424" t="inlineStr">
         <is>
-          <t>[6.    4.935 3.87 ]</t>
+          <t>[[0.0, 0.0, 0.0], [0.0, 0.0, 43.8], [0.0, 0.0, 87.6]]</t>
         </is>
       </c>
       <c r="E424" t="inlineStr">
         <is>
-          <t>1D array of the outer diameter values defined along the tower axis.</t>
+          <t>2D array of the coordinates (x,y,z) of the tower reference axis. The coordinate system is the global coordinate system of OpenFAST: it is placed at tower base with x pointing downwind, y pointing on the side and z pointing vertically upwards. A standard tower configuration will have zero x and y values and positive z values.</t>
         </is>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>tower.cd</t>
+          <t>tower.diameter</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
@@ -10428,22 +9811,26 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D425" t="inlineStr">
         <is>
-          <t>[1. 1. 1.]</t>
+          <t>[6.0, 4.935, 3.87]</t>
         </is>
       </c>
       <c r="E425" t="inlineStr">
         <is>
-          <t>1D array of the drag coefficients defined along the tower height.</t>
+          <t>1D array of the outer diameter values defined along the tower axis.</t>
         </is>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>tower.layer_thickness</t>
+          <t>tower.cd</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
@@ -10451,26 +9838,22 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C426" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C426" t="inlineStr"/>
       <c r="D426" t="inlineStr">
         <is>
-          <t>[[0.027  0.0222 0.019 ]]</t>
+          <t>[1.0, 1.0, 1.0]</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>2D array of the thickness of the layers of the tower structure. The first dimension represents each layer, the second dimension represents each piecewise-constant entry of the tower sections.</t>
+          <t>1D array of the drag coefficients defined along the tower height.</t>
         </is>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
         <is>
-          <t>tower.outfitting_factor</t>
+          <t>tower.layer_thickness</t>
         </is>
       </c>
       <c r="B427" t="inlineStr">
@@ -10478,22 +9861,26 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>[1.07]</t>
+          <t>[[0.027, 0.0222, 0.019000000000000003]]</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Multiplier that accounts for secondary structure mass inside of tower</t>
+          <t>2D array of the thickness of the layers of the tower structure. The first dimension represents each layer, the second dimension represents each piecewise-constant entry of the tower sections.</t>
         </is>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
         <is>
-          <t>tower.layer_name</t>
+          <t>tower.outfitting_factor</t>
         </is>
       </c>
       <c r="B428" t="inlineStr">
@@ -10501,26 +9888,20 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C428" t="inlineStr">
-        <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D428" t="inlineStr">
-        <is>
-          <t>['tower_wall']</t>
-        </is>
+      <c r="C428" t="inlineStr"/>
+      <c r="D428" t="n">
+        <v>1.07</v>
       </c>
       <c r="E428" t="inlineStr">
         <is>
-          <t>1D array of the names of the layers modeled in the tower structure.</t>
+          <t>Multiplier that accounts for secondary structure mass inside of tower</t>
         </is>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
         <is>
-          <t>tower.layer_mat</t>
+          <t>tower.tower_mass_user</t>
         </is>
       </c>
       <c r="B429" t="inlineStr">
@@ -10530,24 +9911,22 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="D429" t="inlineStr">
-        <is>
-          <t>['steel']</t>
-        </is>
+          <t>kg</t>
+        </is>
+      </c>
+      <c r="D429" t="n">
+        <v>0</v>
       </c>
       <c r="E429" t="inlineStr">
         <is>
-          <t>1D array of the names of the materials of each layer modeled in the tower structure.</t>
+          <t>Override bottom-up calculation of total tower mass with this value</t>
         </is>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
         <is>
-          <t>tower_grid.s</t>
+          <t>tower.layer_name</t>
         </is>
       </c>
       <c r="B430" t="inlineStr">
@@ -10555,22 +9934,26 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C430" t="inlineStr"/>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
       <c r="D430" t="inlineStr">
         <is>
-          <t>[0.  0.5 1. ]</t>
+          <t>tower_wall</t>
         </is>
       </c>
       <c r="E430" t="inlineStr">
         <is>
-          <t>1D array of the non-dimensional grid defined along the tower axis (0-tower base, 1-tower top)</t>
+          <t>1D array of the names of the layers modeled in the tower structure.</t>
         </is>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
         <is>
-          <t>tower_grid.height</t>
+          <t>tower.layer_mat</t>
         </is>
       </c>
       <c r="B431" t="inlineStr">
@@ -10580,24 +9963,24 @@
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Scalar of the tower height computed along the z axis.</t>
+          <t>1D array of the names of the materials of each layer modeled in the tower structure.</t>
         </is>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
         <is>
-          <t>tower_grid.length</t>
+          <t>tower_grid.s</t>
         </is>
       </c>
       <c r="B432" t="inlineStr">
@@ -10605,44 +9988,88 @@
           <t>output</t>
         </is>
       </c>
-      <c r="C432" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+      <c r="C432" t="inlineStr"/>
       <c r="D432" t="inlineStr">
         <is>
-          <t>[90.]</t>
+          <t>[0.0, 0.5, 1.0]</t>
         </is>
       </c>
       <c r="E432" t="inlineStr">
         <is>
-          <t>Scalar of the tower length computed along its curved axis. A standard straight tower will be as high as long.</t>
+          <t>1D array of the non-dimensional grid defined along the tower axis (0-tower base, 1-tower top)</t>
         </is>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
+          <t>tower_grid.height</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D433" t="n">
+        <v>90</v>
+      </c>
+      <c r="E433" t="inlineStr">
+        <is>
+          <t>Scalar of the tower height computed along the z axis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>tower_grid.length</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+      <c r="D434" t="n">
+        <v>90</v>
+      </c>
+      <c r="E434" t="inlineStr">
+        <is>
+          <t>Scalar of the tower length computed along its curved axis. A standard straight tower will be as high as long.</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
           <t>tower_grid.foundation_height</t>
         </is>
       </c>
-      <c r="B433" t="inlineStr">
-        <is>
-          <t>output</t>
-        </is>
-      </c>
-      <c r="C433" t="inlineStr">
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>output</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D433" t="inlineStr">
-        <is>
-          <t>[0.]</t>
-        </is>
-      </c>
-      <c r="E433" t="inlineStr">
+      <c r="D435" t="n">
+        <v>0</v>
+      </c>
+      <c r="E435" t="inlineStr">
         <is>
           <t>Foundation height in respect to the ground level.</t>
         </is>
